--- a/SENTIMENT.xlsx
+++ b/SENTIMENT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hbs-my.sharepoint.com/personal/dmangoubi_hbs_edu/Documents/Daniel Projects/Sentiment Index/Data for 2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dmangoubi\Code\Sentiment Index\BW_Index\BakerandWurglerInvestorSentimentIndex\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{C24097EC-2D8C-4F41-BEDC-1C2B076E0838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{351D5935-DA3E-4539-9BBD-3AAB644F34F4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA56141-A551-4C57-8174-01FCD65E7109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -2209,10 +2209,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2531,94 +2527,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>17</v>
       </c>
@@ -2626,7 +2622,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>19</v>
       </c>
@@ -2634,7 +2630,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -2642,7 +2638,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -2650,7 +2646,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -2658,7 +2654,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -2666,7 +2662,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -2674,7 +2670,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -2682,7 +2678,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -2690,7 +2686,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -2698,7 +2694,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -2706,7 +2702,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -2714,7 +2710,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -2722,7 +2718,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -2737,10 +2733,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O805"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O817"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>45</v>
       </c>
@@ -2787,7 +2783,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>195801</v>
       </c>
@@ -2804,7 +2800,7 @@
         <v>28.639999389648438</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>195802</v>
       </c>
@@ -2821,7 +2817,7 @@
         <v>28.700000762939453</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>195803</v>
       </c>
@@ -2838,7 +2834,7 @@
         <v>28.870000839233398</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>195804</v>
       </c>
@@ -2855,7 +2851,7 @@
         <v>28.940000534057617</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>195805</v>
       </c>
@@ -2872,7 +2868,7 @@
         <v>28.940000534057617</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>195806</v>
       </c>
@@ -2889,7 +2885,7 @@
         <v>28.909999847412109</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>195807</v>
       </c>
@@ -2906,7 +2902,7 @@
         <v>28.889999389648438</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>195808</v>
       </c>
@@ -2923,7 +2919,7 @@
         <v>28.940000534057617</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>195809</v>
       </c>
@@ -2940,7 +2936,7 @@
         <v>28.909999847412109</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>195810</v>
       </c>
@@ -2957,7 +2953,7 @@
         <v>28.909999847412109</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>195811</v>
       </c>
@@ -2974,7 +2970,7 @@
         <v>28.950000762939453</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>195812</v>
       </c>
@@ -2994,7 +2990,7 @@
         <v>28.969999313354492</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>195901</v>
       </c>
@@ -3023,7 +3019,7 @@
         <v>29.010000228881836</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>195902</v>
       </c>
@@ -3052,7 +3048,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>195903</v>
       </c>
@@ -3081,7 +3077,7 @@
         <v>28.969999313354492</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>195904</v>
       </c>
@@ -3110,7 +3106,7 @@
         <v>28.979999542236328</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>195905</v>
       </c>
@@ -3139,7 +3135,7 @@
         <v>29.040000915527344</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>195906</v>
       </c>
@@ -3168,7 +3164,7 @@
         <v>29.110000610351563</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>195907</v>
       </c>
@@ -3197,7 +3193,7 @@
         <v>29.149999618530273</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>195908</v>
       </c>
@@ -3226,7 +3222,7 @@
         <v>29.180000305175781</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>195909</v>
       </c>
@@ -3255,7 +3251,7 @@
         <v>29.25</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>195910</v>
       </c>
@@ -3284,7 +3280,7 @@
         <v>29.350000381469727</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>195911</v>
       </c>
@@ -3313,7 +3309,7 @@
         <v>29.350000381469727</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>195912</v>
       </c>
@@ -3342,7 +3338,7 @@
         <v>29.409999847412109</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>196001</v>
       </c>
@@ -3377,7 +3373,7 @@
         <v>29.370000839233398</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>196002</v>
       </c>
@@ -3412,7 +3408,7 @@
         <v>29.409999847412109</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>196003</v>
       </c>
@@ -3447,7 +3443,7 @@
         <v>29.409999847412109</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>196004</v>
       </c>
@@ -3485,7 +3481,7 @@
         <v>29.540000915527344</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>196005</v>
       </c>
@@ -3523,7 +3519,7 @@
         <v>29.569999694824219</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>196006</v>
       </c>
@@ -3561,7 +3557,7 @@
         <v>29.610000610351563</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>196007</v>
       </c>
@@ -3599,7 +3595,7 @@
         <v>29.549999237060547</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>196008</v>
       </c>
@@ -3637,7 +3633,7 @@
         <v>29.610000610351563</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>196009</v>
       </c>
@@ -3675,7 +3671,7 @@
         <v>29.610000610351563</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>196010</v>
       </c>
@@ -3713,7 +3709,7 @@
         <v>29.75</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>196011</v>
       </c>
@@ -3751,7 +3747,7 @@
         <v>29.780000686645508</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>196012</v>
       </c>
@@ -3789,7 +3785,7 @@
         <v>29.809999465942383</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>196101</v>
       </c>
@@ -3827,7 +3823,7 @@
         <v>29.840000152587891</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>196102</v>
       </c>
@@ -3865,7 +3861,7 @@
         <v>29.840000152587891</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>196103</v>
       </c>
@@ -3903,7 +3899,7 @@
         <v>29.840000152587891</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>196104</v>
       </c>
@@ -3941,7 +3937,7 @@
         <v>29.809999465942383</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>196105</v>
       </c>
@@ -3979,7 +3975,7 @@
         <v>29.840000152587891</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>196106</v>
       </c>
@@ -4017,7 +4013,7 @@
         <v>29.840000152587891</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>196107</v>
       </c>
@@ -4055,7 +4051,7 @@
         <v>29.920000076293945</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>196108</v>
       </c>
@@ -4093,7 +4089,7 @@
         <v>29.940000534057617</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>196109</v>
       </c>
@@ -4131,7 +4127,7 @@
         <v>29.979999542236328</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>196110</v>
       </c>
@@ -4169,7 +4165,7 @@
         <v>29.979999542236328</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>196111</v>
       </c>
@@ -4207,7 +4203,7 @@
         <v>29.979999542236328</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>196112</v>
       </c>
@@ -4245,7 +4241,7 @@
         <v>30.010000228881836</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>196201</v>
       </c>
@@ -4283,7 +4279,7 @@
         <v>30.040000915527344</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>196202</v>
       </c>
@@ -4321,7 +4317,7 @@
         <v>30.110000610351563</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>196203</v>
       </c>
@@ -4359,7 +4355,7 @@
         <v>30.170000076293945</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>196204</v>
       </c>
@@ -4397,7 +4393,7 @@
         <v>30.209999084472656</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>196205</v>
       </c>
@@ -4435,7 +4431,7 @@
         <v>30.239999771118164</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>196206</v>
       </c>
@@ -4473,7 +4469,7 @@
         <v>30.209999084472656</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>196207</v>
       </c>
@@ -4511,7 +4507,7 @@
         <v>30.219999313354492</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>196208</v>
       </c>
@@ -4549,7 +4545,7 @@
         <v>30.280000686645508</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>196209</v>
       </c>
@@ -4587,7 +4583,7 @@
         <v>30.420000076293945</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>196210</v>
       </c>
@@ -4625,7 +4621,7 @@
         <v>30.379999160766602</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>196211</v>
       </c>
@@ -4663,7 +4659,7 @@
         <v>30.379999160766602</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>196212</v>
       </c>
@@ -4701,7 +4697,7 @@
         <v>30.379999160766602</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>196301</v>
       </c>
@@ -4739,7 +4735,7 @@
         <v>30.440000534057617</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>196302</v>
       </c>
@@ -4777,7 +4773,7 @@
         <v>30.479999542236328</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>196303</v>
       </c>
@@ -4815,7 +4811,7 @@
         <v>30.510000228881836</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>196304</v>
       </c>
@@ -4853,7 +4849,7 @@
         <v>30.479999542236328</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>196305</v>
       </c>
@@ -4891,7 +4887,7 @@
         <v>30.510000228881836</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>196306</v>
       </c>
@@ -4929,7 +4925,7 @@
         <v>30.610000610351563</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>196307</v>
       </c>
@@ -4967,7 +4963,7 @@
         <v>30.690000534057617</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>196308</v>
       </c>
@@ -5005,7 +5001,7 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>196309</v>
       </c>
@@ -5043,7 +5039,7 @@
         <v>30.719999313354492</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>196310</v>
       </c>
@@ -5081,7 +5077,7 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>196311</v>
       </c>
@@ -5119,7 +5115,7 @@
         <v>30.780000686645508</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>196312</v>
       </c>
@@ -5157,7 +5153,7 @@
         <v>30.879999160766602</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>196401</v>
       </c>
@@ -5195,7 +5191,7 @@
         <v>30.940000534057617</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>196402</v>
       </c>
@@ -5233,7 +5229,7 @@
         <v>30.909999847412109</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>196403</v>
       </c>
@@ -5271,7 +5267,7 @@
         <v>30.940000534057617</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>196404</v>
       </c>
@@ -5309,7 +5305,7 @@
         <v>30.950000762939453</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>196405</v>
       </c>
@@ -5347,7 +5343,7 @@
         <v>30.979999542236328</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>196406</v>
       </c>
@@ -5385,7 +5381,7 @@
         <v>31.010000228881836</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>196407</v>
       </c>
@@ -5423,7 +5419,7 @@
         <v>31.020000457763672</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>196408</v>
       </c>
@@ -5461,7 +5457,7 @@
         <v>31.049999237060547</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>196409</v>
       </c>
@@ -5499,7 +5495,7 @@
         <v>31.079999923706055</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>196410</v>
       </c>
@@ -5537,7 +5533,7 @@
         <v>31.120000839233398</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>196411</v>
       </c>
@@ -5575,7 +5571,7 @@
         <v>31.209999084472656</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>196412</v>
       </c>
@@ -5613,7 +5609,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>196501</v>
       </c>
@@ -5651,7 +5647,7 @@
         <v>31.280000686645508</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>196502</v>
       </c>
@@ -5689,7 +5685,7 @@
         <v>31.280000686645508</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>196503</v>
       </c>
@@ -5727,7 +5723,7 @@
         <v>31.309999465942383</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>196504</v>
       </c>
@@ -5765,7 +5761,7 @@
         <v>31.379999160766602</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>196505</v>
       </c>
@@ -5803,7 +5799,7 @@
         <v>31.479999542236328</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>196506</v>
       </c>
@@ -5841,7 +5837,7 @@
         <v>31.610000610351563</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>196507</v>
       </c>
@@ -5888,7 +5884,7 @@
         <v>31.579999923706055</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>196508</v>
       </c>
@@ -5935,7 +5931,7 @@
         <v>31.549999237060547</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>196509</v>
       </c>
@@ -5982,7 +5978,7 @@
         <v>31.620000839233398</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>196510</v>
       </c>
@@ -6029,7 +6025,7 @@
         <v>31.649999618530273</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>196511</v>
       </c>
@@ -6076,7 +6072,7 @@
         <v>31.75</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>196512</v>
       </c>
@@ -6123,7 +6119,7 @@
         <v>31.850000381469727</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>196601</v>
       </c>
@@ -6170,7 +6166,7 @@
         <v>31.879999160766602</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>196602</v>
       </c>
@@ -6217,7 +6213,7 @@
         <v>32.080001831054688</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>196603</v>
       </c>
@@ -6264,7 +6260,7 @@
         <v>32.180000305175781</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>196604</v>
       </c>
@@ -6311,7 +6307,7 @@
         <v>32.279998779296875</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>196605</v>
       </c>
@@ -6358,7 +6354,7 @@
         <v>32.349998474121094</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>196606</v>
       </c>
@@ -6405,7 +6401,7 @@
         <v>32.380001068115234</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>196607</v>
       </c>
@@ -6452,7 +6448,7 @@
         <v>32.450000762939453</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>196608</v>
       </c>
@@ -6499,7 +6495,7 @@
         <v>32.650001525878906</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>196609</v>
       </c>
@@ -6546,7 +6542,7 @@
         <v>32.75</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>196610</v>
       </c>
@@ -6593,7 +6589,7 @@
         <v>32.849998474121094</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>196611</v>
       </c>
@@ -6640,7 +6636,7 @@
         <v>32.880001068115234</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>196612</v>
       </c>
@@ -6687,7 +6683,7 @@
         <v>32.919998168945313</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>196701</v>
       </c>
@@ -6734,7 +6730,7 @@
         <v>32.900001525878906</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>196702</v>
       </c>
@@ -6781,7 +6777,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>196703</v>
       </c>
@@ -6828,7 +6824,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>196704</v>
       </c>
@@ -6875,7 +6871,7 @@
         <v>33.099998474121094</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>196705</v>
       </c>
@@ -6922,7 +6918,7 @@
         <v>33.099998474121094</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>196706</v>
       </c>
@@ -6969,7 +6965,7 @@
         <v>33.299999237060547</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>196707</v>
       </c>
@@ -7016,7 +7012,7 @@
         <v>33.400001525878906</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>196708</v>
       </c>
@@ -7063,7 +7059,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>196709</v>
       </c>
@@ -7110,7 +7106,7 @@
         <v>33.599998474121094</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>196710</v>
       </c>
@@ -7157,7 +7153,7 @@
         <v>33.700000762939453</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>196711</v>
       </c>
@@ -7204,7 +7200,7 @@
         <v>33.900001525878906</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>196712</v>
       </c>
@@ -7251,7 +7247,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>196801</v>
       </c>
@@ -7298,7 +7294,7 @@
         <v>34.099998474121094</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>196802</v>
       </c>
@@ -7345,7 +7341,7 @@
         <v>34.200000762939453</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>196803</v>
       </c>
@@ -7392,7 +7388,7 @@
         <v>34.299999237060547</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>196804</v>
       </c>
@@ -7439,7 +7435,7 @@
         <v>34.400001525878906</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>196805</v>
       </c>
@@ -7486,7 +7482,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>196806</v>
       </c>
@@ -7533,7 +7529,7 @@
         <v>34.700000762939453</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>196807</v>
       </c>
@@ -7580,7 +7576,7 @@
         <v>34.900001525878906</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>196808</v>
       </c>
@@ -7627,7 +7623,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>196809</v>
       </c>
@@ -7674,7 +7670,7 @@
         <v>35.099998474121094</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>196810</v>
       </c>
@@ -7721,7 +7717,7 @@
         <v>35.299999237060547</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>196811</v>
       </c>
@@ -7768,7 +7764,7 @@
         <v>35.400001525878906</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>196812</v>
       </c>
@@ -7815,7 +7811,7 @@
         <v>35.599998474121094</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>196901</v>
       </c>
@@ -7862,7 +7858,7 @@
         <v>35.700000762939453</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>196902</v>
       </c>
@@ -7909,7 +7905,7 @@
         <v>35.799999237060547</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>196903</v>
       </c>
@@ -7956,7 +7952,7 @@
         <v>36.099998474121094</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>196904</v>
       </c>
@@ -8003,7 +7999,7 @@
         <v>36.299999237060547</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>196905</v>
       </c>
@@ -8050,7 +8046,7 @@
         <v>36.400001525878906</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>196906</v>
       </c>
@@ -8097,7 +8093,7 @@
         <v>36.599998474121094</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>196907</v>
       </c>
@@ -8144,7 +8140,7 @@
         <v>36.799999237060547</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>196908</v>
       </c>
@@ -8191,7 +8187,7 @@
         <v>36.900001525878906</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>196909</v>
       </c>
@@ -8238,7 +8234,7 @@
         <v>37.099998474121094</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>196910</v>
       </c>
@@ -8285,7 +8281,7 @@
         <v>37.299999237060547</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>196911</v>
       </c>
@@ -8332,7 +8328,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>196912</v>
       </c>
@@ -8379,7 +8375,7 @@
         <v>37.700000762939453</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>197001</v>
       </c>
@@ -8426,7 +8422,7 @@
         <v>37.900001525878906</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>197002</v>
       </c>
@@ -8473,7 +8469,7 @@
         <v>38.099998474121094</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>197003</v>
       </c>
@@ -8520,7 +8516,7 @@
         <v>38.299999237060547</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>197004</v>
       </c>
@@ -8567,7 +8563,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>197005</v>
       </c>
@@ -8614,7 +8610,7 @@
         <v>38.599998474121094</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>197006</v>
       </c>
@@ -8661,7 +8657,7 @@
         <v>38.799999237060547</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>197007</v>
       </c>
@@ -8708,7 +8704,7 @@
         <v>38.900001525878906</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>197008</v>
       </c>
@@ -8755,7 +8751,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>197009</v>
       </c>
@@ -8802,7 +8798,7 @@
         <v>39.200000762939453</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>197010</v>
       </c>
@@ -8849,7 +8845,7 @@
         <v>39.400001525878906</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>197011</v>
       </c>
@@ -8896,7 +8892,7 @@
         <v>39.599998474121094</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>197012</v>
       </c>
@@ -8943,7 +8939,7 @@
         <v>39.799999237060547</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>197101</v>
       </c>
@@ -8990,7 +8986,7 @@
         <v>39.900001525878906</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>197102</v>
       </c>
@@ -9037,7 +9033,7 @@
         <v>39.900001525878906</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>197103</v>
       </c>
@@ -9084,7 +9080,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>197104</v>
       </c>
@@ -9131,7 +9127,7 @@
         <v>40.099998474121094</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>197105</v>
       </c>
@@ -9178,7 +9174,7 @@
         <v>40.299999237060547</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>197106</v>
       </c>
@@ -9225,7 +9221,7 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>197107</v>
       </c>
@@ -9272,7 +9268,7 @@
         <v>40.599998474121094</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>197108</v>
       </c>
@@ -9319,7 +9315,7 @@
         <v>40.700000762939453</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>197109</v>
       </c>
@@ -9366,7 +9362,7 @@
         <v>40.799999237060547</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>197110</v>
       </c>
@@ -9413,7 +9409,7 @@
         <v>40.900001525878906</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>197111</v>
       </c>
@@ -9460,7 +9456,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>197112</v>
       </c>
@@ -9507,7 +9503,7 @@
         <v>41.099998474121094</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>197201</v>
       </c>
@@ -9554,7 +9550,7 @@
         <v>41.200000762939453</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>197202</v>
       </c>
@@ -9601,7 +9597,7 @@
         <v>41.400001525878906</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>197203</v>
       </c>
@@ -9648,7 +9644,7 @@
         <v>41.400001525878906</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>197204</v>
       </c>
@@ -9695,7 +9691,7 @@
         <v>41.5</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>197205</v>
       </c>
@@ -9742,7 +9738,7 @@
         <v>41.599998474121094</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>197206</v>
       </c>
@@ -9789,7 +9785,7 @@
         <v>41.700000762939453</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>197207</v>
       </c>
@@ -9836,7 +9832,7 @@
         <v>41.799999237060547</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>197208</v>
       </c>
@@ -9883,7 +9879,7 @@
         <v>41.900001525878906</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>197209</v>
       </c>
@@ -9930,7 +9926,7 @@
         <v>42.099998474121094</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>197210</v>
       </c>
@@ -9977,7 +9973,7 @@
         <v>42.200000762939453</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>197211</v>
       </c>
@@ -10024,7 +10020,7 @@
         <v>42.400001525878906</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>197212</v>
       </c>
@@ -10071,7 +10067,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>197301</v>
       </c>
@@ -10118,7 +10114,7 @@
         <v>42.700000762939453</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>197302</v>
       </c>
@@ -10165,7 +10161,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>197303</v>
       </c>
@@ -10212,7 +10208,7 @@
         <v>43.400001525878906</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>197304</v>
       </c>
@@ -10259,7 +10255,7 @@
         <v>43.700000762939453</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>197305</v>
       </c>
@@ -10306,7 +10302,7 @@
         <v>43.900001525878906</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>197306</v>
       </c>
@@ -10353,7 +10349,7 @@
         <v>44.200000762939453</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>197307</v>
       </c>
@@ -10400,7 +10396,7 @@
         <v>44.200000762939453</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>197308</v>
       </c>
@@ -10447,7 +10443,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>197309</v>
       </c>
@@ -10494,7 +10490,7 @@
         <v>45.200000762939453</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>197310</v>
       </c>
@@ -10541,7 +10537,7 @@
         <v>45.599998474121094</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>197311</v>
       </c>
@@ -10588,7 +10584,7 @@
         <v>45.900001525878906</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>197312</v>
       </c>
@@ -10632,7 +10628,7 @@
         <v>46.299999237060547</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>197401</v>
       </c>
@@ -10676,7 +10672,7 @@
         <v>46.799999237060547</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>197402</v>
       </c>
@@ -10723,7 +10719,7 @@
         <v>47.299999237060547</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>197403</v>
       </c>
@@ -10770,7 +10766,7 @@
         <v>47.799999237060547</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>197404</v>
       </c>
@@ -10814,7 +10810,7 @@
         <v>48.099998474121094</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197405</v>
       </c>
@@ -10858,7 +10854,7 @@
         <v>48.599998474121094</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>197406</v>
       </c>
@@ -10905,7 +10901,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>197407</v>
       </c>
@@ -10949,7 +10945,7 @@
         <v>49.299999237060547</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>197408</v>
       </c>
@@ -10993,7 +10989,7 @@
         <v>49.900001525878906</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>197409</v>
       </c>
@@ -11037,7 +11033,7 @@
         <v>50.599998474121094</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>197410</v>
       </c>
@@ -11081,7 +11077,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>197411</v>
       </c>
@@ -11125,7 +11121,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>197412</v>
       </c>
@@ -11169,7 +11165,7 @@
         <v>51.900001525878906</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>197501</v>
       </c>
@@ -11216,7 +11212,7 @@
         <v>52.299999237060547</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>197502</v>
       </c>
@@ -11263,7 +11259,7 @@
         <v>52.599998474121094</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>197503</v>
       </c>
@@ -11307,7 +11303,7 @@
         <v>52.799999237060547</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>197504</v>
       </c>
@@ -11351,7 +11347,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>197505</v>
       </c>
@@ -11395,7 +11391,7 @@
         <v>53.099998474121094</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>197506</v>
       </c>
@@ -11442,7 +11438,7 @@
         <v>53.5</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>197507</v>
       </c>
@@ -11489,7 +11485,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>197508</v>
       </c>
@@ -11536,7 +11532,7 @@
         <v>54.200000762939453</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>197509</v>
       </c>
@@ -11583,7 +11579,7 @@
         <v>54.599998474121094</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>197510</v>
       </c>
@@ -11630,7 +11626,7 @@
         <v>54.900001525878906</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>197511</v>
       </c>
@@ -11677,7 +11673,7 @@
         <v>55.299999237060547</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>197512</v>
       </c>
@@ -11724,7 +11720,7 @@
         <v>55.599998474121094</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>197601</v>
       </c>
@@ -11771,7 +11767,7 @@
         <v>55.799999237060547</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>197602</v>
       </c>
@@ -11818,7 +11814,7 @@
         <v>55.900001525878906</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>197603</v>
       </c>
@@ -11865,7 +11861,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>197604</v>
       </c>
@@ -11909,7 +11905,7 @@
         <v>56.099998474121094</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>197605</v>
       </c>
@@ -11956,7 +11952,7 @@
         <v>56.400001525878906</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>197606</v>
       </c>
@@ -12003,7 +11999,7 @@
         <v>56.700000762939453</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>197607</v>
       </c>
@@ -12050,7 +12046,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>197608</v>
       </c>
@@ -12097,7 +12093,7 @@
         <v>57.299999237060547</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>197609</v>
       </c>
@@ -12144,7 +12140,7 @@
         <v>57.599998474121094</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>197610</v>
       </c>
@@ -12191,7 +12187,7 @@
         <v>57.900001525878906</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>197611</v>
       </c>
@@ -12238,7 +12234,7 @@
         <v>58.099998474121094</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>197612</v>
       </c>
@@ -12285,7 +12281,7 @@
         <v>58.400001525878906</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>197701</v>
       </c>
@@ -12332,7 +12328,7 @@
         <v>58.700000762939453</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>197702</v>
       </c>
@@ -12379,7 +12375,7 @@
         <v>59.299999237060547</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>197703</v>
       </c>
@@ -12426,7 +12422,7 @@
         <v>59.599998474121094</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>197704</v>
       </c>
@@ -12473,7 +12469,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>197705</v>
       </c>
@@ -12520,7 +12516,7 @@
         <v>60.200000762939453</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>197706</v>
       </c>
@@ -12567,7 +12563,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>197707</v>
       </c>
@@ -12614,7 +12610,7 @@
         <v>60.799999237060547</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>197708</v>
       </c>
@@ -12661,7 +12657,7 @@
         <v>61.099998474121094</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>197709</v>
       </c>
@@ -12708,7 +12704,7 @@
         <v>61.299999237060547</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>197710</v>
       </c>
@@ -12755,7 +12751,7 @@
         <v>61.599998474121094</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>197711</v>
       </c>
@@ -12802,7 +12798,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>197712</v>
       </c>
@@ -12849,7 +12845,7 @@
         <v>62.299999237060547</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>197801</v>
       </c>
@@ -12896,7 +12892,7 @@
         <v>62.700000762939453</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>197802</v>
       </c>
@@ -12943,7 +12939,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>197803</v>
       </c>
@@ -12990,7 +12986,7 @@
         <v>63.400001525878906</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>197804</v>
       </c>
@@ -13037,7 +13033,7 @@
         <v>63.900001525878906</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>197805</v>
       </c>
@@ -13084,7 +13080,7 @@
         <v>64.5</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>197806</v>
       </c>
@@ -13131,7 +13127,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>197807</v>
       </c>
@@ -13178,7 +13174,7 @@
         <v>65.5</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>197808</v>
       </c>
@@ -13225,7 +13221,7 @@
         <v>65.900001525878906</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>197809</v>
       </c>
@@ -13272,7 +13268,7 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>197810</v>
       </c>
@@ -13319,7 +13315,7 @@
         <v>67.099998474121094</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>197811</v>
       </c>
@@ -13366,7 +13362,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>197812</v>
       </c>
@@ -13413,7 +13409,7 @@
         <v>67.900001525878906</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>197901</v>
       </c>
@@ -13460,7 +13456,7 @@
         <v>68.5</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>197902</v>
       </c>
@@ -13507,7 +13503,7 @@
         <v>69.199996948242188</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>197903</v>
       </c>
@@ -13554,7 +13550,7 @@
         <v>69.900001525878906</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>197904</v>
       </c>
@@ -13601,7 +13597,7 @@
         <v>70.599998474121094</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>197905</v>
       </c>
@@ -13648,7 +13644,7 @@
         <v>71.400001525878906</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>197906</v>
       </c>
@@ -13695,7 +13691,7 @@
         <v>72.199996948242188</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>197907</v>
       </c>
@@ -13742,7 +13738,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>197908</v>
       </c>
@@ -13789,7 +13785,7 @@
         <v>73.699996948242188</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>197909</v>
       </c>
@@ -13836,7 +13832,7 @@
         <v>74.400001525878906</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>197910</v>
       </c>
@@ -13883,7 +13879,7 @@
         <v>75.199996948242188</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>197911</v>
       </c>
@@ -13930,7 +13926,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>197912</v>
       </c>
@@ -13977,7 +13973,7 @@
         <v>76.900001525878906</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>198001</v>
       </c>
@@ -14024,7 +14020,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>198002</v>
       </c>
@@ -14071,7 +14067,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>198003</v>
       </c>
@@ -14118,7 +14114,7 @@
         <v>80.099998474121094</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>198004</v>
       </c>
@@ -14165,7 +14161,7 @@
         <v>80.900001525878906</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>198005</v>
       </c>
@@ -14212,7 +14208,7 @@
         <v>81.699996948242188</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>198006</v>
       </c>
@@ -14259,7 +14255,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>198007</v>
       </c>
@@ -14306,7 +14302,7 @@
         <v>82.599998474121094</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>198008</v>
       </c>
@@ -14353,7 +14349,7 @@
         <v>83.199996948242188</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>198009</v>
       </c>
@@ -14400,7 +14396,7 @@
         <v>83.900001525878906</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>198010</v>
       </c>
@@ -14447,7 +14443,7 @@
         <v>84.699996948242188</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>198011</v>
       </c>
@@ -14494,7 +14490,7 @@
         <v>85.599998474121094</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>198012</v>
       </c>
@@ -14541,7 +14537,7 @@
         <v>86.400001525878906</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>198101</v>
       </c>
@@ -14588,7 +14584,7 @@
         <v>87.199996948242188</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>198102</v>
       </c>
@@ -14635,7 +14631,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>198103</v>
       </c>
@@ -14682,7 +14678,7 @@
         <v>88.599998474121094</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>198104</v>
       </c>
@@ -14729,7 +14725,7 @@
         <v>89.099998474121094</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>198105</v>
       </c>
@@ -14776,7 +14772,7 @@
         <v>89.699996948242188</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>198106</v>
       </c>
@@ -14823,7 +14819,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>198107</v>
       </c>
@@ -14870,7 +14866,7 @@
         <v>91.5</v>
       </c>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>198108</v>
       </c>
@@ -14917,7 +14913,7 @@
         <v>92.199996948242188</v>
       </c>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>198109</v>
       </c>
@@ -14964,7 +14960,7 @@
         <v>93.099998474121094</v>
       </c>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>198110</v>
       </c>
@@ -15011,7 +15007,7 @@
         <v>93.400001525878906</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>198111</v>
       </c>
@@ -15058,7 +15054,7 @@
         <v>93.800003051757813</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>198112</v>
       </c>
@@ -15105,7 +15101,7 @@
         <v>94.099998474121094</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>198201</v>
       </c>
@@ -15152,7 +15148,7 @@
         <v>94.400001525878906</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>198202</v>
       </c>
@@ -15199,7 +15195,7 @@
         <v>94.699996948242188</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>198203</v>
       </c>
@@ -15246,7 +15242,7 @@
         <v>94.699996948242188</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>198204</v>
       </c>
@@ -15293,7 +15289,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>198205</v>
       </c>
@@ -15340,7 +15336,7 @@
         <v>95.900001525878906</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>198206</v>
       </c>
@@ -15387,7 +15383,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>198207</v>
       </c>
@@ -15434,7 +15430,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>198208</v>
       </c>
@@ -15481,7 +15477,7 @@
         <v>97.699996948242188</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>198209</v>
       </c>
@@ -15528,7 +15524,7 @@
         <v>97.699996948242188</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>198210</v>
       </c>
@@ -15575,7 +15571,7 @@
         <v>98.099998474121094</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>198211</v>
       </c>
@@ -15622,7 +15618,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>198212</v>
       </c>
@@ -15669,7 +15665,7 @@
         <v>97.699996948242188</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>198301</v>
       </c>
@@ -15716,7 +15712,7 @@
         <v>97.900001525878906</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>198302</v>
       </c>
@@ -15763,7 +15759,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>198303</v>
       </c>
@@ -15810,7 +15806,7 @@
         <v>98.099998474121094</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>198304</v>
       </c>
@@ -15857,7 +15853,7 @@
         <v>98.800003051757813</v>
       </c>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>198305</v>
       </c>
@@ -15904,7 +15900,7 @@
         <v>99.199996948242188</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>198306</v>
       </c>
@@ -15951,7 +15947,7 @@
         <v>99.400001525878906</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>198307</v>
       </c>
@@ -15998,7 +15994,7 @@
         <v>99.800003051757813</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>198308</v>
       </c>
@@ -16045,7 +16041,7 @@
         <v>100.09999847412109</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>198309</v>
       </c>
@@ -16092,7 +16088,7 @@
         <v>100.40000152587891</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>198310</v>
       </c>
@@ -16139,7 +16135,7 @@
         <v>100.80000305175781</v>
       </c>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>198311</v>
       </c>
@@ -16186,7 +16182,7 @@
         <v>101.09999847412109</v>
       </c>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>198312</v>
       </c>
@@ -16233,7 +16229,7 @@
         <v>101.40000152587891</v>
       </c>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>198401</v>
       </c>
@@ -16280,7 +16276,7 @@
         <v>102.09999847412109</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>198402</v>
       </c>
@@ -16327,7 +16323,7 @@
         <v>102.59999847412109</v>
       </c>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>198403</v>
       </c>
@@ -16374,7 +16370,7 @@
         <v>102.90000152587891</v>
       </c>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>198404</v>
       </c>
@@ -16421,7 +16417,7 @@
         <v>103.30000305175781</v>
       </c>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>198405</v>
       </c>
@@ -16468,7 +16464,7 @@
         <v>103.5</v>
       </c>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>198406</v>
       </c>
@@ -16515,7 +16511,7 @@
         <v>103.69999694824219</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>198407</v>
       </c>
@@ -16562,7 +16558,7 @@
         <v>104.09999847412109</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>198408</v>
       </c>
@@ -16609,7 +16605,7 @@
         <v>104.40000152587891</v>
       </c>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>198409</v>
       </c>
@@ -16656,7 +16652,7 @@
         <v>104.69999694824219</v>
       </c>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>198410</v>
       </c>
@@ -16703,7 +16699,7 @@
         <v>105.09999847412109</v>
       </c>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>198411</v>
       </c>
@@ -16750,7 +16746,7 @@
         <v>105.30000305175781</v>
       </c>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>198412</v>
       </c>
@@ -16797,7 +16793,7 @@
         <v>105.5</v>
       </c>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>198501</v>
       </c>
@@ -16844,7 +16840,7 @@
         <v>105.69999694824219</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>198502</v>
       </c>
@@ -16891,7 +16887,7 @@
         <v>106.30000305175781</v>
       </c>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>198503</v>
       </c>
@@ -16938,7 +16934,7 @@
         <v>106.80000305175781</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>198504</v>
       </c>
@@ -16985,7 +16981,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>198505</v>
       </c>
@@ -17032,7 +17028,7 @@
         <v>107.19999694824219</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>198506</v>
       </c>
@@ -17079,7 +17075,7 @@
         <v>107.5</v>
       </c>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>198507</v>
       </c>
@@ -17126,7 +17122,7 @@
         <v>107.69999694824219</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>198508</v>
       </c>
@@ -17173,7 +17169,7 @@
         <v>107.90000152587891</v>
       </c>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>198509</v>
       </c>
@@ -17220,7 +17216,7 @@
         <v>108.09999847412109</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>198510</v>
       </c>
@@ -17267,7 +17263,7 @@
         <v>108.5</v>
       </c>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>198511</v>
       </c>
@@ -17314,7 +17310,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>198512</v>
       </c>
@@ -17361,7 +17357,7 @@
         <v>109.5</v>
       </c>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>198601</v>
       </c>
@@ -17408,7 +17404,7 @@
         <v>109.90000152587891</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>198602</v>
       </c>
@@ -17455,7 +17451,7 @@
         <v>109.69999694824219</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>198603</v>
       </c>
@@ -17502,7 +17498,7 @@
         <v>109.09999847412109</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>198604</v>
       </c>
@@ -17549,7 +17545,7 @@
         <v>108.69999694824219</v>
       </c>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>198605</v>
       </c>
@@ -17596,7 +17592,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>198606</v>
       </c>
@@ -17643,7 +17639,7 @@
         <v>109.40000152587891</v>
       </c>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>198607</v>
       </c>
@@ -17690,7 +17686,7 @@
         <v>109.5</v>
       </c>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>198608</v>
       </c>
@@ -17737,7 +17733,7 @@
         <v>109.59999847412109</v>
       </c>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>198609</v>
       </c>
@@ -17784,7 +17780,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>198610</v>
       </c>
@@ -17831,7 +17827,7 @@
         <v>110.19999694824219</v>
       </c>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>198611</v>
       </c>
@@ -17878,7 +17874,7 @@
         <v>110.40000152587891</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>198612</v>
       </c>
@@ -17925,7 +17921,7 @@
         <v>110.80000305175781</v>
       </c>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>198701</v>
       </c>
@@ -17972,7 +17968,7 @@
         <v>111.40000152587891</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>198702</v>
       </c>
@@ -18019,7 +18015,7 @@
         <v>111.80000305175781</v>
       </c>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>198703</v>
       </c>
@@ -18066,7 +18062,7 @@
         <v>112.19999694824219</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>198704</v>
       </c>
@@ -18113,7 +18109,7 @@
         <v>112.69999694824219</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>198705</v>
       </c>
@@ -18160,7 +18156,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>198706</v>
       </c>
@@ -18207,7 +18203,7 @@
         <v>113.5</v>
       </c>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>198707</v>
       </c>
@@ -18254,7 +18250,7 @@
         <v>113.80000305175781</v>
       </c>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>198708</v>
       </c>
@@ -18301,7 +18297,7 @@
         <v>114.30000305175781</v>
       </c>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>198709</v>
       </c>
@@ -18348,7 +18344,7 @@
         <v>114.69999694824219</v>
       </c>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>198710</v>
       </c>
@@ -18395,7 +18391,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>198711</v>
       </c>
@@ -18442,7 +18438,7 @@
         <v>115.40000152587891</v>
       </c>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>198712</v>
       </c>
@@ -18486,7 +18482,7 @@
         <v>115.59999847412109</v>
       </c>
     </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>198801</v>
       </c>
@@ -18533,7 +18529,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>198802</v>
       </c>
@@ -18580,7 +18576,7 @@
         <v>116.19999694824219</v>
       </c>
     </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>198803</v>
       </c>
@@ -18627,7 +18623,7 @@
         <v>116.5</v>
       </c>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>198804</v>
       </c>
@@ -18674,7 +18670,7 @@
         <v>117.19999694824219</v>
       </c>
     </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>198805</v>
       </c>
@@ -18721,7 +18717,7 @@
         <v>117.5</v>
       </c>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>198806</v>
       </c>
@@ -18768,7 +18764,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>198807</v>
       </c>
@@ -18815,7 +18811,7 @@
         <v>118.5</v>
       </c>
     </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>198808</v>
       </c>
@@ -18862,7 +18858,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="370" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>198809</v>
       </c>
@@ -18909,7 +18905,7 @@
         <v>119.5</v>
       </c>
     </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>198810</v>
       </c>
@@ -18956,7 +18952,7 @@
         <v>119.90000152587891</v>
       </c>
     </row>
-    <row r="372" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>198811</v>
       </c>
@@ -19003,7 +18999,7 @@
         <v>120.30000305175781</v>
       </c>
     </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>198812</v>
       </c>
@@ -19050,7 +19046,7 @@
         <v>120.69999694824219</v>
       </c>
     </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>198901</v>
       </c>
@@ -19097,7 +19093,7 @@
         <v>121.19999694824219</v>
       </c>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>198902</v>
       </c>
@@ -19144,7 +19140,7 @@
         <v>121.59999847412109</v>
       </c>
     </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>198903</v>
       </c>
@@ -19191,7 +19187,7 @@
         <v>122.19999694824219</v>
       </c>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>198904</v>
       </c>
@@ -19238,7 +19234,7 @@
         <v>123.09999847412109</v>
       </c>
     </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>198905</v>
       </c>
@@ -19285,7 +19281,7 @@
         <v>123.69999694824219</v>
       </c>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>198906</v>
       </c>
@@ -19332,7 +19328,7 @@
         <v>124.09999847412109</v>
       </c>
     </row>
-    <row r="380" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>198907</v>
       </c>
@@ -19379,7 +19375,7 @@
         <v>124.5</v>
       </c>
     </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>198908</v>
       </c>
@@ -19426,7 +19422,7 @@
         <v>124.5</v>
       </c>
     </row>
-    <row r="382" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>198909</v>
       </c>
@@ -19473,7 +19469,7 @@
         <v>124.80000305175781</v>
       </c>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>198910</v>
       </c>
@@ -19520,7 +19516,7 @@
         <v>125.40000152587891</v>
       </c>
     </row>
-    <row r="384" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>198911</v>
       </c>
@@ -19567,7 +19563,7 @@
         <v>125.90000152587891</v>
       </c>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>198912</v>
       </c>
@@ -19614,7 +19610,7 @@
         <v>126.30000305175781</v>
       </c>
     </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>199001</v>
       </c>
@@ -19661,7 +19657,7 @@
         <v>127.5</v>
       </c>
     </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>199002</v>
       </c>
@@ -19708,7 +19704,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>199003</v>
       </c>
@@ -19755,7 +19751,7 @@
         <v>128.60000610351563</v>
       </c>
     </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>199004</v>
       </c>
@@ -19802,7 +19798,7 @@
         <v>128.89999389648438</v>
       </c>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>199005</v>
       </c>
@@ -19849,7 +19845,7 @@
         <v>129.10000610351563</v>
       </c>
     </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>199006</v>
       </c>
@@ -19896,7 +19892,7 @@
         <v>129.89999389648438</v>
       </c>
     </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>199007</v>
       </c>
@@ -19943,7 +19939,7 @@
         <v>130.5</v>
       </c>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>199008</v>
       </c>
@@ -19990,7 +19986,7 @@
         <v>131.60000610351563</v>
       </c>
     </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>199009</v>
       </c>
@@ -20037,7 +20033,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>199010</v>
       </c>
@@ -20084,7 +20080,7 @@
         <v>133.39999389648438</v>
       </c>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>199011</v>
       </c>
@@ -20128,7 +20124,7 @@
         <v>133.69999694824219</v>
       </c>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>199012</v>
       </c>
@@ -20175,7 +20171,7 @@
         <v>134.19999694824219</v>
       </c>
     </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>199101</v>
       </c>
@@ -20222,7 +20218,7 @@
         <v>134.69999694824219</v>
       </c>
     </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>199102</v>
       </c>
@@ -20269,7 +20265,7 @@
         <v>134.80000305175781</v>
       </c>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>199103</v>
       </c>
@@ -20316,7 +20312,7 @@
         <v>134.80000305175781</v>
       </c>
     </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>199104</v>
       </c>
@@ -20363,7 +20359,7 @@
         <v>135.10000610351563</v>
       </c>
     </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>199105</v>
       </c>
@@ -20410,7 +20406,7 @@
         <v>135.60000610351563</v>
       </c>
     </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>199106</v>
       </c>
@@ -20457,7 +20453,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>199107</v>
       </c>
@@ -20504,7 +20500,7 @@
         <v>136.19999694824219</v>
       </c>
     </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>199108</v>
       </c>
@@ -20551,7 +20547,7 @@
         <v>136.60000610351563</v>
       </c>
     </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>199109</v>
       </c>
@@ -20598,7 +20594,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>199110</v>
       </c>
@@ -20645,7 +20641,7 @@
         <v>137.19999694824219</v>
       </c>
     </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>199111</v>
       </c>
@@ -20692,7 +20688,7 @@
         <v>137.80000305175781</v>
       </c>
     </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>199112</v>
       </c>
@@ -20739,7 +20735,7 @@
         <v>138.19999694824219</v>
       </c>
     </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>199201</v>
       </c>
@@ -20786,7 +20782,7 @@
         <v>138.30000305175781</v>
       </c>
     </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>199202</v>
       </c>
@@ -20833,7 +20829,7 @@
         <v>138.60000610351563</v>
       </c>
     </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>199203</v>
       </c>
@@ -20880,7 +20876,7 @@
         <v>139.10000610351563</v>
       </c>
     </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>199204</v>
       </c>
@@ -20927,7 +20923,7 @@
         <v>139.39999389648438</v>
       </c>
     </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>199205</v>
       </c>
@@ -20974,7 +20970,7 @@
         <v>139.69999694824219</v>
       </c>
     </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>199206</v>
       </c>
@@ -21021,7 +21017,7 @@
         <v>140.10000610351563</v>
       </c>
     </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>199207</v>
       </c>
@@ -21068,7 +21064,7 @@
         <v>140.5</v>
       </c>
     </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>199208</v>
       </c>
@@ -21115,7 +21111,7 @@
         <v>140.80000305175781</v>
       </c>
     </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>199209</v>
       </c>
@@ -21162,7 +21158,7 @@
         <v>141.10000610351563</v>
       </c>
     </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>199210</v>
       </c>
@@ -21209,7 +21205,7 @@
         <v>141.69999694824219</v>
       </c>
     </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>199211</v>
       </c>
@@ -21256,7 +21252,7 @@
         <v>142.10000610351563</v>
       </c>
     </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>199212</v>
       </c>
@@ -21303,7 +21299,7 @@
         <v>142.30000305175781</v>
       </c>
     </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>199301</v>
       </c>
@@ -21350,7 +21346,7 @@
         <v>142.80000305175781</v>
       </c>
     </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>199302</v>
       </c>
@@ -21397,7 +21393,7 @@
         <v>143.10000610351563</v>
       </c>
     </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>199303</v>
       </c>
@@ -21444,7 +21440,7 @@
         <v>143.30000305175781</v>
       </c>
     </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>199304</v>
       </c>
@@ -21491,7 +21487,7 @@
         <v>143.80000305175781</v>
       </c>
     </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>199305</v>
       </c>
@@ -21538,7 +21534,7 @@
         <v>144.19999694824219</v>
       </c>
     </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>199306</v>
       </c>
@@ -21585,7 +21581,7 @@
         <v>144.30000305175781</v>
       </c>
     </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>199307</v>
       </c>
@@ -21632,7 +21628,7 @@
         <v>144.5</v>
       </c>
     </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>199308</v>
       </c>
@@ -21679,7 +21675,7 @@
         <v>144.80000305175781</v>
       </c>
     </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>199309</v>
       </c>
@@ -21726,7 +21722,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>199310</v>
       </c>
@@ -21773,7 +21769,7 @@
         <v>145.60000610351563</v>
       </c>
     </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>199311</v>
       </c>
@@ -21820,7 +21816,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="433" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>199312</v>
       </c>
@@ -21867,7 +21863,7 @@
         <v>146.30000305175781</v>
       </c>
     </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>199401</v>
       </c>
@@ -21914,7 +21910,7 @@
         <v>146.30000305175781</v>
       </c>
     </row>
-    <row r="435" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>199402</v>
       </c>
@@ -21961,7 +21957,7 @@
         <v>146.69999694824219</v>
       </c>
     </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>199403</v>
       </c>
@@ -22008,7 +22004,7 @@
         <v>147.10000610351563</v>
       </c>
     </row>
-    <row r="437" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>199404</v>
       </c>
@@ -22055,7 +22051,7 @@
         <v>147.19999694824219</v>
       </c>
     </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>199405</v>
       </c>
@@ -22102,7 +22098,7 @@
         <v>147.5</v>
       </c>
     </row>
-    <row r="439" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>199406</v>
       </c>
@@ -22149,7 +22145,7 @@
         <v>147.89999389648438</v>
       </c>
     </row>
-    <row r="440" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>199407</v>
       </c>
@@ -22196,7 +22192,7 @@
         <v>148.39999389648438</v>
       </c>
     </row>
-    <row r="441" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>199408</v>
       </c>
@@ -22243,7 +22239,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="442" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>199409</v>
       </c>
@@ -22290,7 +22286,7 @@
         <v>149.30000305175781</v>
       </c>
     </row>
-    <row r="443" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>199410</v>
       </c>
@@ -22337,7 +22333,7 @@
         <v>149.39999389648438</v>
       </c>
     </row>
-    <row r="444" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>199411</v>
       </c>
@@ -22384,7 +22380,7 @@
         <v>149.80000305175781</v>
       </c>
     </row>
-    <row r="445" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>199412</v>
       </c>
@@ -22431,7 +22427,7 @@
         <v>150.10000610351563</v>
       </c>
     </row>
-    <row r="446" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>199501</v>
       </c>
@@ -22478,7 +22474,7 @@
         <v>150.5</v>
       </c>
     </row>
-    <row r="447" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>199502</v>
       </c>
@@ -22525,7 +22521,7 @@
         <v>150.89999389648438</v>
       </c>
     </row>
-    <row r="448" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>199503</v>
       </c>
@@ -22572,7 +22568,7 @@
         <v>151.19999694824219</v>
       </c>
     </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>199504</v>
       </c>
@@ -22619,7 +22615,7 @@
         <v>151.80000305175781</v>
       </c>
     </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>199505</v>
       </c>
@@ -22666,7 +22662,7 @@
         <v>152.10000610351563</v>
       </c>
     </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>199506</v>
       </c>
@@ -22713,7 +22709,7 @@
         <v>152.39999389648438</v>
       </c>
     </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>199507</v>
       </c>
@@ -22760,7 +22756,7 @@
         <v>152.60000610351563</v>
       </c>
     </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>199508</v>
       </c>
@@ -22807,7 +22803,7 @@
         <v>152.89999389648438</v>
       </c>
     </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>199509</v>
       </c>
@@ -22854,7 +22850,7 @@
         <v>153.10000610351563</v>
       </c>
     </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>199510</v>
       </c>
@@ -22901,7 +22897,7 @@
         <v>153.5</v>
       </c>
     </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>199511</v>
       </c>
@@ -22948,7 +22944,7 @@
         <v>153.69999694824219</v>
       </c>
     </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>199512</v>
       </c>
@@ -22995,7 +22991,7 @@
         <v>153.89999389648438</v>
       </c>
     </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>199601</v>
       </c>
@@ -23042,7 +23038,7 @@
         <v>154.69999694824219</v>
       </c>
     </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>199602</v>
       </c>
@@ -23089,7 +23085,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>199603</v>
       </c>
@@ -23136,7 +23132,7 @@
         <v>155.5</v>
       </c>
     </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>199604</v>
       </c>
@@ -23183,7 +23179,7 @@
         <v>156.10000610351563</v>
       </c>
     </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>199605</v>
       </c>
@@ -23230,7 +23226,7 @@
         <v>156.39999389648438</v>
       </c>
     </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>199606</v>
       </c>
@@ -23277,7 +23273,7 @@
         <v>156.69999694824219</v>
       </c>
     </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>199607</v>
       </c>
@@ -23324,7 +23320,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>199608</v>
       </c>
@@ -23371,7 +23367,7 @@
         <v>157.19999694824219</v>
       </c>
     </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>199609</v>
       </c>
@@ -23418,7 +23414,7 @@
         <v>157.69999694824219</v>
       </c>
     </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>199610</v>
       </c>
@@ -23465,7 +23461,7 @@
         <v>158.19999694824219</v>
       </c>
     </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>199611</v>
       </c>
@@ -23512,7 +23508,7 @@
         <v>158.69999694824219</v>
       </c>
     </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>199612</v>
       </c>
@@ -23559,7 +23555,7 @@
         <v>159.10000610351563</v>
       </c>
     </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>199701</v>
       </c>
@@ -23606,7 +23602,7 @@
         <v>159.39999389648438</v>
       </c>
     </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>199702</v>
       </c>
@@ -23653,7 +23649,7 @@
         <v>159.69999694824219</v>
       </c>
     </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>199703</v>
       </c>
@@ -23700,7 +23696,7 @@
         <v>159.80000305175781</v>
       </c>
     </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>199704</v>
       </c>
@@ -23747,7 +23743,7 @@
         <v>159.89999389648438</v>
       </c>
     </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>199705</v>
       </c>
@@ -23794,7 +23790,7 @@
         <v>159.89999389648438</v>
       </c>
     </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>199706</v>
       </c>
@@ -23841,7 +23837,7 @@
         <v>160.19999694824219</v>
       </c>
     </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>199707</v>
       </c>
@@ -23888,7 +23884,7 @@
         <v>160.39999389648438</v>
       </c>
     </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>199708</v>
       </c>
@@ -23935,7 +23931,7 @@
         <v>160.80000305175781</v>
       </c>
     </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>199709</v>
       </c>
@@ -23982,7 +23978,7 @@
         <v>161.19999694824219</v>
       </c>
     </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>199710</v>
       </c>
@@ -24029,7 +24025,7 @@
         <v>161.5</v>
       </c>
     </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>199711</v>
       </c>
@@ -24076,7 +24072,7 @@
         <v>161.69999694824219</v>
       </c>
     </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>199712</v>
       </c>
@@ -24123,7 +24119,7 @@
         <v>161.80000305175781</v>
       </c>
     </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>199801</v>
       </c>
@@ -24170,7 +24166,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>199802</v>
       </c>
@@ -24217,7 +24213,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>199803</v>
       </c>
@@ -24264,7 +24260,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>199804</v>
       </c>
@@ -24311,7 +24307,7 @@
         <v>162.19999694824219</v>
       </c>
     </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>199805</v>
       </c>
@@ -24358,7 +24354,7 @@
         <v>162.60000610351563</v>
       </c>
     </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>199806</v>
       </c>
@@ -24405,7 +24401,7 @@
         <v>162.80000305175781</v>
       </c>
     </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>199807</v>
       </c>
@@ -24452,7 +24448,7 @@
         <v>163.19999694824219</v>
       </c>
     </row>
-    <row r="489" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>199808</v>
       </c>
@@ -24499,7 +24495,7 @@
         <v>163.39999389648438</v>
       </c>
     </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>199809</v>
       </c>
@@ -24546,7 +24542,7 @@
         <v>163.5</v>
       </c>
     </row>
-    <row r="491" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>199810</v>
       </c>
@@ -24593,7 +24589,7 @@
         <v>163.89999389648438</v>
       </c>
     </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>199811</v>
       </c>
@@ -24640,7 +24636,7 @@
         <v>164.10000610351563</v>
       </c>
     </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>199812</v>
       </c>
@@ -24687,7 +24683,7 @@
         <v>164.39999389648438</v>
       </c>
     </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>199901</v>
       </c>
@@ -24734,7 +24730,7 @@
         <v>164.69999694824219</v>
       </c>
     </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>199902</v>
       </c>
@@ -24781,7 +24777,7 @@
         <v>164.69999694824219</v>
       </c>
     </row>
-    <row r="496" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>199903</v>
       </c>
@@ -24828,7 +24824,7 @@
         <v>164.80000305175781</v>
       </c>
     </row>
-    <row r="497" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>199904</v>
       </c>
@@ -24875,7 +24871,7 @@
         <v>165.89999389648438</v>
       </c>
     </row>
-    <row r="498" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>199905</v>
       </c>
@@ -24922,7 +24918,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="499" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>199906</v>
       </c>
@@ -24969,7 +24965,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="500" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>199907</v>
       </c>
@@ -25016,7 +25012,7 @@
         <v>166.69999694824219</v>
       </c>
     </row>
-    <row r="501" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>199908</v>
       </c>
@@ -25063,7 +25059,7 @@
         <v>167.10000610351563</v>
       </c>
     </row>
-    <row r="502" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>199909</v>
       </c>
@@ -25110,7 +25106,7 @@
         <v>167.80000305175781</v>
       </c>
     </row>
-    <row r="503" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>199910</v>
       </c>
@@ -25157,7 +25153,7 @@
         <v>168.10000610351563</v>
       </c>
     </row>
-    <row r="504" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>199911</v>
       </c>
@@ -25204,7 +25200,7 @@
         <v>168.39999389648438</v>
       </c>
     </row>
-    <row r="505" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>199912</v>
       </c>
@@ -25251,7 +25247,7 @@
         <v>168.80000305175781</v>
       </c>
     </row>
-    <row r="506" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>200001</v>
       </c>
@@ -25298,7 +25294,7 @@
         <v>169.30000305175781</v>
       </c>
     </row>
-    <row r="507" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>200002</v>
       </c>
@@ -25345,7 +25341,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="508" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>200003</v>
       </c>
@@ -25392,7 +25388,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="509" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>200004</v>
       </c>
@@ -25439,7 +25435,7 @@
         <v>170.89999389648438</v>
       </c>
     </row>
-    <row r="510" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>200005</v>
       </c>
@@ -25486,7 +25482,7 @@
         <v>171.19999694824219</v>
       </c>
     </row>
-    <row r="511" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>200006</v>
       </c>
@@ -25533,7 +25529,7 @@
         <v>172.19999694824219</v>
       </c>
     </row>
-    <row r="512" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>200007</v>
       </c>
@@ -25580,7 +25576,7 @@
         <v>172.69999694824219</v>
       </c>
     </row>
-    <row r="513" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>200008</v>
       </c>
@@ -25627,7 +25623,7 @@
         <v>172.69999694824219</v>
       </c>
     </row>
-    <row r="514" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>200009</v>
       </c>
@@ -25674,7 +25670,7 @@
         <v>173.60000610351563</v>
       </c>
     </row>
-    <row r="515" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>200010</v>
       </c>
@@ -25721,7 +25717,7 @@
         <v>173.89999389648438</v>
       </c>
     </row>
-    <row r="516" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>200011</v>
       </c>
@@ -25768,7 +25764,7 @@
         <v>174.19999694824219</v>
       </c>
     </row>
-    <row r="517" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>200012</v>
       </c>
@@ -25815,7 +25811,7 @@
         <v>174.60000610351563</v>
       </c>
     </row>
-    <row r="518" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>200101</v>
       </c>
@@ -25862,7 +25858,7 @@
         <v>175.60000610351563</v>
       </c>
     </row>
-    <row r="519" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>200102</v>
       </c>
@@ -25909,7 +25905,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="520" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>200103</v>
       </c>
@@ -25956,7 +25952,7 @@
         <v>176.10000610351563</v>
       </c>
     </row>
-    <row r="521" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>200104</v>
       </c>
@@ -26003,7 +25999,7 @@
         <v>176.39999389648438</v>
       </c>
     </row>
-    <row r="522" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>200105</v>
       </c>
@@ -26050,7 +26046,7 @@
         <v>177.30000305175781</v>
       </c>
     </row>
-    <row r="523" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>200106</v>
       </c>
@@ -26097,7 +26093,7 @@
         <v>177.69999694824219</v>
       </c>
     </row>
-    <row r="524" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>200107</v>
       </c>
@@ -26144,7 +26140,7 @@
         <v>177.39999389648438</v>
       </c>
     </row>
-    <row r="525" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>200108</v>
       </c>
@@ -26191,7 +26187,7 @@
         <v>177.39999389648438</v>
       </c>
     </row>
-    <row r="526" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>200109</v>
       </c>
@@ -26235,7 +26231,7 @@
         <v>178.10000610351563</v>
       </c>
     </row>
-    <row r="527" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>200110</v>
       </c>
@@ -26282,7 +26278,7 @@
         <v>177.60000610351563</v>
       </c>
     </row>
-    <row r="528" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>200111</v>
       </c>
@@ -26329,7 +26325,7 @@
         <v>177.5</v>
       </c>
     </row>
-    <row r="529" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>200112</v>
       </c>
@@ -26376,7 +26372,7 @@
         <v>177.39999389648438</v>
       </c>
     </row>
-    <row r="530" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>200201</v>
       </c>
@@ -26423,7 +26419,7 @@
         <v>177.69999694824219</v>
       </c>
     </row>
-    <row r="531" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>200202</v>
       </c>
@@ -26470,7 +26466,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="532" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>200203</v>
       </c>
@@ -26517,7 +26513,7 @@
         <v>178.5</v>
       </c>
     </row>
-    <row r="533" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>200204</v>
       </c>
@@ -26564,7 +26560,7 @@
         <v>179.30000305175781</v>
       </c>
     </row>
-    <row r="534" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>200205</v>
       </c>
@@ -26611,7 +26607,7 @@
         <v>179.5</v>
       </c>
     </row>
-    <row r="535" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>200206</v>
       </c>
@@ -26658,7 +26654,7 @@
         <v>179.60000610351563</v>
       </c>
     </row>
-    <row r="536" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>200207</v>
       </c>
@@ -26705,7 +26701,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="537" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>200208</v>
       </c>
@@ -26749,7 +26745,7 @@
         <v>180.5</v>
       </c>
     </row>
-    <row r="538" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>200209</v>
       </c>
@@ -26793,7 +26789,7 @@
         <v>180.80000305175781</v>
       </c>
     </row>
-    <row r="539" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>200210</v>
       </c>
@@ -26840,7 +26836,7 @@
         <v>181.19999694824219</v>
       </c>
     </row>
-    <row r="540" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>200211</v>
       </c>
@@ -26887,7 +26883,7 @@
         <v>181.5</v>
       </c>
     </row>
-    <row r="541" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>200212</v>
       </c>
@@ -26934,7 +26930,7 @@
         <v>181.80000305175781</v>
       </c>
     </row>
-    <row r="542" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>200301</v>
       </c>
@@ -26978,7 +26974,7 @@
         <v>182.60000610351563</v>
       </c>
     </row>
-    <row r="543" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>200302</v>
       </c>
@@ -27025,7 +27021,7 @@
         <v>183.60000610351563</v>
       </c>
     </row>
-    <row r="544" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>200303</v>
       </c>
@@ -27069,7 +27065,7 @@
         <v>183.89999389648438</v>
       </c>
     </row>
-    <row r="545" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>200304</v>
       </c>
@@ -27113,7 +27109,7 @@
         <v>183.19999694824219</v>
       </c>
     </row>
-    <row r="546" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>200305</v>
       </c>
@@ -27160,7 +27156,7 @@
         <v>182.89999389648438</v>
       </c>
     </row>
-    <row r="547" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>200306</v>
       </c>
@@ -27207,7 +27203,7 @@
         <v>183.10000610351563</v>
       </c>
     </row>
-    <row r="548" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>200307</v>
       </c>
@@ -27254,7 +27250,7 @@
         <v>183.69999694824219</v>
       </c>
     </row>
-    <row r="549" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>200308</v>
       </c>
@@ -27301,7 +27297,7 @@
         <v>184.5</v>
       </c>
     </row>
-    <row r="550" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>200309</v>
       </c>
@@ -27348,7 +27344,7 @@
         <v>185.10000610351563</v>
       </c>
     </row>
-    <row r="551" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>200310</v>
       </c>
@@ -27395,7 +27391,7 @@
         <v>184.89999389648438</v>
       </c>
     </row>
-    <row r="552" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>200311</v>
       </c>
@@ -27442,7 +27438,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="553" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>200312</v>
       </c>
@@ -27489,7 +27485,7 @@
         <v>185.5</v>
       </c>
     </row>
-    <row r="554" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>200401</v>
       </c>
@@ -27536,7 +27532,7 @@
         <v>186.30000305175781</v>
       </c>
     </row>
-    <row r="555" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>200402</v>
       </c>
@@ -27583,7 +27579,7 @@
         <v>186.69999694824219</v>
       </c>
     </row>
-    <row r="556" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>200403</v>
       </c>
@@ -27630,7 +27626,7 @@
         <v>187.10000610351563</v>
       </c>
     </row>
-    <row r="557" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>200404</v>
       </c>
@@ -27677,7 +27673,7 @@
         <v>187.39999389648438</v>
       </c>
     </row>
-    <row r="558" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>200405</v>
       </c>
@@ -27724,7 +27720,7 @@
         <v>188.19999694824219</v>
       </c>
     </row>
-    <row r="559" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>200406</v>
       </c>
@@ -27771,7 +27767,7 @@
         <v>188.89999389648438</v>
       </c>
     </row>
-    <row r="560" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>200407</v>
       </c>
@@ -27818,7 +27814,7 @@
         <v>189.10000610351563</v>
       </c>
     </row>
-    <row r="561" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>200408</v>
       </c>
@@ -27865,7 +27861,7 @@
         <v>189.19999694824219</v>
       </c>
     </row>
-    <row r="562" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>200409</v>
       </c>
@@ -27912,7 +27908,7 @@
         <v>189.80000305175781</v>
       </c>
     </row>
-    <row r="563" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>200410</v>
       </c>
@@ -27959,7 +27955,7 @@
         <v>190.80000305175781</v>
       </c>
     </row>
-    <row r="564" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>200411</v>
       </c>
@@ -28006,7 +28002,7 @@
         <v>191.69999694824219</v>
       </c>
     </row>
-    <row r="565" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>200412</v>
       </c>
@@ -28053,7 +28049,7 @@
         <v>191.69999694824219</v>
       </c>
     </row>
-    <row r="566" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>200501</v>
       </c>
@@ -28100,7 +28096,7 @@
         <v>191.60000610351563</v>
       </c>
     </row>
-    <row r="567" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>200502</v>
       </c>
@@ -28147,7 +28143,7 @@
         <v>192.39999389648438</v>
       </c>
     </row>
-    <row r="568" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>200503</v>
       </c>
@@ -28194,7 +28190,7 @@
         <v>193.10000610351563</v>
       </c>
     </row>
-    <row r="569" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>200504</v>
       </c>
@@ -28241,7 +28237,7 @@
         <v>193.69999694824219</v>
       </c>
     </row>
-    <row r="570" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>200505</v>
       </c>
@@ -28288,7 +28284,7 @@
         <v>193.60000610351563</v>
       </c>
     </row>
-    <row r="571" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>200506</v>
       </c>
@@ -28335,7 +28331,7 @@
         <v>193.69999694824219</v>
       </c>
     </row>
-    <row r="572" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>200507</v>
       </c>
@@ -28382,7 +28378,7 @@
         <v>194.89999389648438</v>
       </c>
     </row>
-    <row r="573" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>200508</v>
       </c>
@@ -28429,7 +28425,7 @@
         <v>196.10000610351563</v>
       </c>
     </row>
-    <row r="574" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>200509</v>
       </c>
@@ -28476,7 +28472,7 @@
         <v>198.80000305175781</v>
       </c>
     </row>
-    <row r="575" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>200510</v>
       </c>
@@ -28523,7 +28519,7 @@
         <v>199.10000610351563</v>
       </c>
     </row>
-    <row r="576" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>200511</v>
       </c>
@@ -28570,7 +28566,7 @@
         <v>198.10000610351563</v>
       </c>
     </row>
-    <row r="577" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>200512</v>
       </c>
@@ -28617,7 +28613,7 @@
         <v>198.10000610351563</v>
       </c>
     </row>
-    <row r="578" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A578">
         <v>200601</v>
       </c>
@@ -28664,7 +28660,7 @@
         <v>199.30000305175781</v>
       </c>
     </row>
-    <row r="579" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>200602</v>
       </c>
@@ -28711,7 +28707,7 @@
         <v>199.39999389648438</v>
       </c>
     </row>
-    <row r="580" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>200603</v>
       </c>
@@ -28758,7 +28754,7 @@
         <v>199.69999694824219</v>
       </c>
     </row>
-    <row r="581" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>200604</v>
       </c>
@@ -28805,7 +28801,7 @@
         <v>200.69999694824219</v>
       </c>
     </row>
-    <row r="582" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A582">
         <v>200605</v>
       </c>
@@ -28852,7 +28848,7 @@
         <v>201.30000305175781</v>
       </c>
     </row>
-    <row r="583" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>200606</v>
       </c>
@@ -28899,7 +28895,7 @@
         <v>201.80000305175781</v>
       </c>
     </row>
-    <row r="584" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A584">
         <v>200607</v>
       </c>
@@ -28946,7 +28942,7 @@
         <v>202.89999389648438</v>
       </c>
     </row>
-    <row r="585" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>200608</v>
       </c>
@@ -28993,7 +28989,7 @@
         <v>203.80000305175781</v>
       </c>
     </row>
-    <row r="586" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>200609</v>
       </c>
@@ -29040,7 +29036,7 @@
         <v>202.80000305175781</v>
       </c>
     </row>
-    <row r="587" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>200610</v>
       </c>
@@ -29087,7 +29083,7 @@
         <v>201.89999389648438</v>
       </c>
     </row>
-    <row r="588" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A588">
         <v>200611</v>
       </c>
@@ -29134,7 +29130,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="589" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>200612</v>
       </c>
@@ -29181,7 +29177,7 @@
         <v>203.10000610351563</v>
       </c>
     </row>
-    <row r="590" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A590">
         <v>200701</v>
       </c>
@@ -29228,7 +29224,7 @@
         <v>203.43699645996094</v>
       </c>
     </row>
-    <row r="591" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>200702</v>
       </c>
@@ -29275,7 +29271,7 @@
         <v>204.22599792480469</v>
       </c>
     </row>
-    <row r="592" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A592">
         <v>200703</v>
       </c>
@@ -29322,7 +29318,7 @@
         <v>205.28799438476563</v>
       </c>
     </row>
-    <row r="593" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A593">
         <v>200704</v>
       </c>
@@ -29369,7 +29365,7 @@
         <v>205.90400695800781</v>
       </c>
     </row>
-    <row r="594" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A594">
         <v>200705</v>
       </c>
@@ -29416,7 +29412,7 @@
         <v>206.7550048828125</v>
       </c>
     </row>
-    <row r="595" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A595">
         <v>200706</v>
       </c>
@@ -29463,7 +29459,7 @@
         <v>207.23399353027344</v>
       </c>
     </row>
-    <row r="596" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A596">
         <v>200707</v>
       </c>
@@ -29510,7 +29506,7 @@
         <v>207.60299682617188</v>
       </c>
     </row>
-    <row r="597" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A597">
         <v>200708</v>
       </c>
@@ -29557,7 +29553,7 @@
         <v>207.66700744628906</v>
       </c>
     </row>
-    <row r="598" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A598">
         <v>200709</v>
       </c>
@@ -29604,7 +29600,7 @@
         <v>208.5469970703125</v>
       </c>
     </row>
-    <row r="599" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A599">
         <v>200710</v>
       </c>
@@ -29651,7 +29647,7 @@
         <v>209.19000244140625</v>
       </c>
     </row>
-    <row r="600" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A600">
         <v>200711</v>
       </c>
@@ -29698,7 +29694,7 @@
         <v>210.83399963378906</v>
       </c>
     </row>
-    <row r="601" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A601">
         <v>200712</v>
       </c>
@@ -29745,7 +29741,7 @@
         <v>211.44500732421875</v>
       </c>
     </row>
-    <row r="602" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A602">
         <v>200801</v>
       </c>
@@ -29792,7 +29788,7 @@
         <v>212.17399597167969</v>
       </c>
     </row>
-    <row r="603" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A603">
         <v>200802</v>
       </c>
@@ -29839,7 +29835,7 @@
         <v>212.68699645996094</v>
       </c>
     </row>
-    <row r="604" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A604">
         <v>200803</v>
       </c>
@@ -29886,7 +29882,7 @@
         <v>213.447998046875</v>
       </c>
     </row>
-    <row r="605" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A605">
         <v>200804</v>
       </c>
@@ -29933,7 +29929,7 @@
         <v>213.94200134277344</v>
       </c>
     </row>
-    <row r="606" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A606">
         <v>200805</v>
       </c>
@@ -29980,7 +29976,7 @@
         <v>215.20799255371094</v>
       </c>
     </row>
-    <row r="607" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A607">
         <v>200806</v>
       </c>
@@ -30027,7 +30023,7 @@
         <v>217.46299743652344</v>
       </c>
     </row>
-    <row r="608" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A608">
         <v>200807</v>
       </c>
@@ -30074,7 +30070,7 @@
         <v>219.01600646972656</v>
       </c>
     </row>
-    <row r="609" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A609">
         <v>200808</v>
       </c>
@@ -30121,7 +30117,7 @@
         <v>218.69000244140625</v>
       </c>
     </row>
-    <row r="610" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A610">
         <v>200809</v>
       </c>
@@ -30165,7 +30161,7 @@
         <v>218.87699890136719</v>
       </c>
     </row>
-    <row r="611" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A611">
         <v>200810</v>
       </c>
@@ -30209,7 +30205,7 @@
         <v>216.9949951171875</v>
       </c>
     </row>
-    <row r="612" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A612">
         <v>200811</v>
       </c>
@@ -30256,7 +30252,7 @@
         <v>213.15299987792969</v>
       </c>
     </row>
-    <row r="613" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A613">
         <v>200812</v>
       </c>
@@ -30300,7 +30296,7 @@
         <v>211.39799499511719</v>
       </c>
     </row>
-    <row r="614" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A614">
         <v>200901</v>
       </c>
@@ -30344,7 +30340,7 @@
         <v>211.93299865722656</v>
       </c>
     </row>
-    <row r="615" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A615">
         <v>200902</v>
       </c>
@@ -30391,7 +30387,7 @@
         <v>212.70500183105469</v>
       </c>
     </row>
-    <row r="616" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A616">
         <v>200903</v>
       </c>
@@ -30435,7 +30431,7 @@
         <v>212.4949951171875</v>
       </c>
     </row>
-    <row r="617" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A617">
         <v>200904</v>
       </c>
@@ -30482,7 +30478,7 @@
         <v>212.70899963378906</v>
       </c>
     </row>
-    <row r="618" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A618">
         <v>200905</v>
       </c>
@@ -30529,7 +30525,7 @@
         <v>213.02200317382813</v>
       </c>
     </row>
-    <row r="619" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A619">
         <v>200906</v>
       </c>
@@ -30576,7 +30572,7 @@
         <v>214.78999328613281</v>
       </c>
     </row>
-    <row r="620" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A620">
         <v>200907</v>
       </c>
@@ -30620,7 +30616,7 @@
         <v>214.72599792480469</v>
       </c>
     </row>
-    <row r="621" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A621">
         <v>200908</v>
       </c>
@@ -30667,7 +30663,7 @@
         <v>215.44500732421875</v>
       </c>
     </row>
-    <row r="622" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A622">
         <v>200909</v>
       </c>
@@ -30714,7 +30710,7 @@
         <v>215.86099243164063</v>
       </c>
     </row>
-    <row r="623" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A623">
         <v>200910</v>
       </c>
@@ -30761,7 +30757,7 @@
         <v>216.50900268554688</v>
       </c>
     </row>
-    <row r="624" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A624">
         <v>200911</v>
       </c>
@@ -30808,7 +30804,7 @@
         <v>217.23399353027344</v>
       </c>
     </row>
-    <row r="625" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A625">
         <v>200912</v>
       </c>
@@ -30855,7 +30851,7 @@
         <v>217.34700012207031</v>
       </c>
     </row>
-    <row r="626" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A626">
         <v>201001</v>
       </c>
@@ -30902,7 +30898,7 @@
         <v>217.48800659179688</v>
       </c>
     </row>
-    <row r="627" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A627">
         <v>201002</v>
       </c>
@@ -30949,7 +30945,7 @@
         <v>217.281005859375</v>
       </c>
     </row>
-    <row r="628" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A628">
         <v>201003</v>
       </c>
@@ -30996,7 +30992,7 @@
         <v>217.35299682617188</v>
       </c>
     </row>
-    <row r="629" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A629">
         <v>201004</v>
       </c>
@@ -31043,7 +31039,7 @@
         <v>217.40299987792969</v>
       </c>
     </row>
-    <row r="630" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A630">
         <v>201005</v>
       </c>
@@ -31090,7 +31086,7 @@
         <v>217.28999328613281</v>
       </c>
     </row>
-    <row r="631" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A631">
         <v>201006</v>
       </c>
@@ -31137,7 +31133,7 @@
         <v>217.19900512695313</v>
       </c>
     </row>
-    <row r="632" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A632">
         <v>201007</v>
       </c>
@@ -31184,7 +31180,7 @@
         <v>217.60499572753906</v>
       </c>
     </row>
-    <row r="633" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A633">
         <v>201008</v>
       </c>
@@ -31231,7 +31227,7 @@
         <v>217.92300415039063</v>
       </c>
     </row>
-    <row r="634" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A634">
         <v>201009</v>
       </c>
@@ -31278,7 +31274,7 @@
         <v>218.27499389648438</v>
       </c>
     </row>
-    <row r="635" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A635">
         <v>201010</v>
       </c>
@@ -31325,7 +31321,7 @@
         <v>219.03500366210938</v>
       </c>
     </row>
-    <row r="636" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A636">
         <v>201011</v>
       </c>
@@ -31372,7 +31368,7 @@
         <v>219.58999633789063</v>
       </c>
     </row>
-    <row r="637" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A637">
         <v>201012</v>
       </c>
@@ -31419,7 +31415,7 @@
         <v>220.47200012207031</v>
       </c>
     </row>
-    <row r="638" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A638">
         <v>201101</v>
       </c>
@@ -31466,7 +31462,7 @@
         <v>221.18699645996094</v>
       </c>
     </row>
-    <row r="639" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A639">
         <v>201102</v>
       </c>
@@ -31513,7 +31509,7 @@
         <v>221.89799499511719</v>
       </c>
     </row>
-    <row r="640" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A640">
         <v>201103</v>
       </c>
@@ -31560,7 +31556,7 @@
         <v>223.04600524902344</v>
       </c>
     </row>
-    <row r="641" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A641">
         <v>201104</v>
       </c>
@@ -31607,7 +31603,7 @@
         <v>224.09300231933594</v>
       </c>
     </row>
-    <row r="642" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A642">
         <v>201105</v>
       </c>
@@ -31654,7 +31650,7 @@
         <v>224.80599975585938</v>
       </c>
     </row>
-    <row r="643" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A643">
         <v>201106</v>
       </c>
@@ -31701,7 +31697,7 @@
         <v>224.80599975585938</v>
       </c>
     </row>
-    <row r="644" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A644">
         <v>201107</v>
       </c>
@@ -31748,7 +31744,7 @@
         <v>225.39500427246094</v>
       </c>
     </row>
-    <row r="645" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A645">
         <v>201108</v>
       </c>
@@ -31795,7 +31791,7 @@
         <v>226.10600280761719</v>
       </c>
     </row>
-    <row r="646" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A646">
         <v>201109</v>
       </c>
@@ -31839,7 +31835,7 @@
         <v>226.59700012207031</v>
       </c>
     </row>
-    <row r="647" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A647">
         <v>201110</v>
       </c>
@@ -31886,7 +31882,7 @@
         <v>226.75</v>
       </c>
     </row>
-    <row r="648" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A648">
         <v>201111</v>
       </c>
@@ -31933,7 +31929,7 @@
         <v>227.16900634765625</v>
       </c>
     </row>
-    <row r="649" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A649">
         <v>201112</v>
       </c>
@@ -31980,7 +31976,7 @@
         <v>227.22300720214844</v>
       </c>
     </row>
-    <row r="650" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A650">
         <v>201201</v>
       </c>
@@ -32027,7 +32023,7 @@
         <v>227.84199523925781</v>
       </c>
     </row>
-    <row r="651" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A651">
         <v>201202</v>
       </c>
@@ -32074,7 +32070,7 @@
         <v>228.32899475097656</v>
       </c>
     </row>
-    <row r="652" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A652">
         <v>201203</v>
       </c>
@@ -32121,7 +32117,7 @@
         <v>228.8070068359375</v>
       </c>
     </row>
-    <row r="653" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A653">
         <v>201204</v>
       </c>
@@ -32168,7 +32164,7 @@
         <v>229.18699645996094</v>
       </c>
     </row>
-    <row r="654" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A654">
         <v>201205</v>
       </c>
@@ -32215,7 +32211,7 @@
         <v>228.71299743652344</v>
       </c>
     </row>
-    <row r="655" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A655">
         <v>201206</v>
       </c>
@@ -32262,7 +32258,7 @@
         <v>228.52400207519531</v>
       </c>
     </row>
-    <row r="656" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A656">
         <v>201207</v>
       </c>
@@ -32309,7 +32305,7 @@
         <v>228.58999633789063</v>
       </c>
     </row>
-    <row r="657" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A657">
         <v>201208</v>
       </c>
@@ -32356,7 +32352,7 @@
         <v>229.91799926757813</v>
       </c>
     </row>
-    <row r="658" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A658">
         <v>201209</v>
       </c>
@@ -32403,7 +32399,7 @@
         <v>231.01499938964844</v>
       </c>
     </row>
-    <row r="659" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A659">
         <v>201210</v>
       </c>
@@ -32450,7 +32446,7 @@
         <v>231.63800048828125</v>
       </c>
     </row>
-    <row r="660" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A660">
         <v>201211</v>
       </c>
@@ -32497,7 +32493,7 @@
         <v>231.24899291992188</v>
       </c>
     </row>
-    <row r="661" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A661">
         <v>201212</v>
       </c>
@@ -32544,7 +32540,7 @@
         <v>231.22099304199219</v>
       </c>
     </row>
-    <row r="662" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A662">
         <v>201301</v>
       </c>
@@ -32591,7 +32587,7 @@
         <v>231.67900085449219</v>
       </c>
     </row>
-    <row r="663" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A663">
         <v>201302</v>
       </c>
@@ -32638,7 +32634,7 @@
         <v>232.93699645996094</v>
       </c>
     </row>
-    <row r="664" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A664">
         <v>201303</v>
       </c>
@@ -32685,7 +32681,7 @@
         <v>232.28199768066406</v>
       </c>
     </row>
-    <row r="665" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A665">
         <v>201304</v>
       </c>
@@ -32732,7 +32728,7 @@
         <v>231.7969970703125</v>
       </c>
     </row>
-    <row r="666" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A666">
         <v>201305</v>
       </c>
@@ -32779,7 +32775,7 @@
         <v>231.89300537109375</v>
       </c>
     </row>
-    <row r="667" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A667">
         <v>201306</v>
       </c>
@@ -32826,7 +32822,7 @@
         <v>232.44500732421875</v>
       </c>
     </row>
-    <row r="668" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A668">
         <v>201307</v>
       </c>
@@ -32873,7 +32869,7 @@
         <v>232.89999389648438</v>
       </c>
     </row>
-    <row r="669" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A669">
         <v>201308</v>
       </c>
@@ -32920,7 +32916,7 @@
         <v>233.45599365234375</v>
       </c>
     </row>
-    <row r="670" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A670">
         <v>201309</v>
       </c>
@@ -32967,7 +32963,7 @@
         <v>233.54400634765625</v>
       </c>
     </row>
-    <row r="671" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A671">
         <v>201310</v>
       </c>
@@ -33014,7 +33010,7 @@
         <v>233.66900634765625</v>
       </c>
     </row>
-    <row r="672" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A672">
         <v>201311</v>
       </c>
@@ -33061,7 +33057,7 @@
         <v>234.10000610351563</v>
       </c>
     </row>
-    <row r="673" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A673">
         <v>201312</v>
       </c>
@@ -33108,7 +33104,7 @@
         <v>234.718994140625</v>
       </c>
     </row>
-    <row r="674" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A674">
         <v>201401</v>
       </c>
@@ -33155,7 +33151,7 @@
         <v>235.28799438476563</v>
       </c>
     </row>
-    <row r="675" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A675">
         <v>201402</v>
       </c>
@@ -33202,7 +33198,7 @@
         <v>235.5469970703125</v>
       </c>
     </row>
-    <row r="676" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A676">
         <v>201403</v>
       </c>
@@ -33249,7 +33245,7 @@
         <v>236.02799987792969</v>
       </c>
     </row>
-    <row r="677" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A677">
         <v>201404</v>
       </c>
@@ -33296,7 +33292,7 @@
         <v>236.46800231933594</v>
       </c>
     </row>
-    <row r="678" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A678">
         <v>201405</v>
       </c>
@@ -33343,7 +33339,7 @@
         <v>236.91799926757813</v>
       </c>
     </row>
-    <row r="679" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A679">
         <v>201406</v>
       </c>
@@ -33390,7 +33386,7 @@
         <v>237.23100280761719</v>
       </c>
     </row>
-    <row r="680" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A680">
         <v>201407</v>
       </c>
@@ -33437,7 +33433,7 @@
         <v>237.49800109863281</v>
       </c>
     </row>
-    <row r="681" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A681">
         <v>201408</v>
       </c>
@@ -33484,7 +33480,7 @@
         <v>237.46000671386719</v>
       </c>
     </row>
-    <row r="682" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A682">
         <v>201409</v>
       </c>
@@ -33531,7 +33527,7 @@
         <v>237.47700500488281</v>
       </c>
     </row>
-    <row r="683" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A683">
         <v>201410</v>
       </c>
@@ -33578,7 +33574,7 @@
         <v>237.42999267578125</v>
       </c>
     </row>
-    <row r="684" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A684">
         <v>201411</v>
       </c>
@@ -33625,7 +33621,7 @@
         <v>236.98300170898438</v>
       </c>
     </row>
-    <row r="685" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A685">
         <v>201412</v>
       </c>
@@ -33672,7 +33668,7 @@
         <v>236.25199890136719</v>
       </c>
     </row>
-    <row r="686" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A686">
         <v>201501</v>
       </c>
@@ -33719,7 +33715,7 @@
         <v>234.74699401855469</v>
       </c>
     </row>
-    <row r="687" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A687">
         <v>201502</v>
       </c>
@@ -33766,7 +33762,7 @@
         <v>235.34199523925781</v>
       </c>
     </row>
-    <row r="688" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A688">
         <v>201503</v>
       </c>
@@ -33813,7 +33809,7 @@
         <v>235.97599792480469</v>
       </c>
     </row>
-    <row r="689" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A689">
         <v>201504</v>
       </c>
@@ -33860,7 +33856,7 @@
         <v>236.22200012207031</v>
       </c>
     </row>
-    <row r="690" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A690">
         <v>201505</v>
       </c>
@@ -33907,7 +33903,7 @@
         <v>237.00100708007813</v>
       </c>
     </row>
-    <row r="691" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A691">
         <v>201506</v>
       </c>
@@ -33954,7 +33950,7 @@
         <v>237.65699768066406</v>
       </c>
     </row>
-    <row r="692" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A692">
         <v>201507</v>
       </c>
@@ -34001,7 +33997,7 @@
         <v>238.03399658203125</v>
       </c>
     </row>
-    <row r="693" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A693">
         <v>201508</v>
       </c>
@@ -34048,7 +34044,7 @@
         <v>238.03300476074219</v>
       </c>
     </row>
-    <row r="694" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A694">
         <v>201509</v>
       </c>
@@ -34095,7 +34091,7 @@
         <v>237.49800109863281</v>
       </c>
     </row>
-    <row r="695" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A695">
         <v>201510</v>
       </c>
@@ -34142,7 +34138,7 @@
         <v>237.73300170898438</v>
       </c>
     </row>
-    <row r="696" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A696">
         <v>201511</v>
       </c>
@@ -34189,7 +34185,7 @@
         <v>238.01699829101563</v>
       </c>
     </row>
-    <row r="697" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A697">
         <v>201512</v>
       </c>
@@ -34236,7 +34232,7 @@
         <v>237.76100158691406</v>
       </c>
     </row>
-    <row r="698" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A698">
         <v>201601</v>
       </c>
@@ -34280,7 +34276,7 @@
         <v>237.65199279785156</v>
       </c>
     </row>
-    <row r="699" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A699">
         <v>201602</v>
       </c>
@@ -34327,7 +34323,7 @@
         <v>237.33599853515625</v>
       </c>
     </row>
-    <row r="700" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A700">
         <v>201603</v>
       </c>
@@ -34374,7 +34370,7 @@
         <v>238.08000183105469</v>
       </c>
     </row>
-    <row r="701" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A701">
         <v>201604</v>
       </c>
@@ -34421,7 +34417,7 @@
         <v>238.99200439453125</v>
       </c>
     </row>
-    <row r="702" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A702">
         <v>201605</v>
       </c>
@@ -34468,7 +34464,7 @@
         <v>239.5570068359375</v>
       </c>
     </row>
-    <row r="703" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A703">
         <v>201606</v>
       </c>
@@ -34515,7 +34511,7 @@
         <v>240.22200012207031</v>
       </c>
     </row>
-    <row r="704" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A704">
         <v>201607</v>
       </c>
@@ -34562,7 +34558,7 @@
         <v>240.10099792480469</v>
       </c>
     </row>
-    <row r="705" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A705">
         <v>201608</v>
       </c>
@@ -34609,7 +34605,7 @@
         <v>240.54499816894531</v>
       </c>
     </row>
-    <row r="706" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A706">
         <v>201609</v>
       </c>
@@ -34656,7 +34652,7 @@
         <v>241.17599487304688</v>
       </c>
     </row>
-    <row r="707" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A707">
         <v>201610</v>
       </c>
@@ -34703,7 +34699,7 @@
         <v>241.74099731445313</v>
       </c>
     </row>
-    <row r="708" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A708">
         <v>201611</v>
       </c>
@@ -34750,7 +34746,7 @@
         <v>242.0260009765625</v>
       </c>
     </row>
-    <row r="709" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A709">
         <v>201612</v>
       </c>
@@ -34797,7 +34793,7 @@
         <v>242.63699340820313</v>
       </c>
     </row>
-    <row r="710" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A710">
         <v>201701</v>
       </c>
@@ -34844,7 +34840,7 @@
         <v>243.61799621582031</v>
       </c>
     </row>
-    <row r="711" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A711">
         <v>201702</v>
       </c>
@@ -34891,7 +34887,7 @@
         <v>244.00599670410156</v>
       </c>
     </row>
-    <row r="712" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A712">
         <v>201703</v>
       </c>
@@ -34938,7 +34934,7 @@
         <v>243.89199829101563</v>
       </c>
     </row>
-    <row r="713" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A713">
         <v>201704</v>
       </c>
@@ -34985,7 +34981,7 @@
         <v>244.1929931640625</v>
       </c>
     </row>
-    <row r="714" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A714">
         <v>201705</v>
       </c>
@@ -35032,7 +35028,7 @@
         <v>244.00399780273438</v>
       </c>
     </row>
-    <row r="715" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A715">
         <v>201706</v>
       </c>
@@ -35079,7 +35075,7 @@
         <v>244.16299438476563</v>
       </c>
     </row>
-    <row r="716" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A716">
         <v>201707</v>
       </c>
@@ -35126,7 +35122,7 @@
         <v>244.24299621582031</v>
       </c>
     </row>
-    <row r="717" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A717">
         <v>201708</v>
       </c>
@@ -35173,7 +35169,7 @@
         <v>245.18299865722656</v>
       </c>
     </row>
-    <row r="718" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A718">
         <v>201709</v>
       </c>
@@ -35220,7 +35216,7 @@
         <v>246.43499755859375</v>
       </c>
     </row>
-    <row r="719" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A719">
         <v>201710</v>
       </c>
@@ -35267,7 +35263,7 @@
         <v>246.62600708007813</v>
       </c>
     </row>
-    <row r="720" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A720">
         <v>201711</v>
       </c>
@@ -35314,7 +35310,7 @@
         <v>247.28399658203125</v>
       </c>
     </row>
-    <row r="721" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A721">
         <v>201712</v>
       </c>
@@ -35361,7 +35357,7 @@
         <v>247.80499267578125</v>
       </c>
     </row>
-    <row r="722" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A722">
         <v>201801</v>
       </c>
@@ -35408,7 +35404,7 @@
         <v>248.85899353027344</v>
       </c>
     </row>
-    <row r="723" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A723">
         <v>201802</v>
       </c>
@@ -35455,7 +35451,7 @@
         <v>249.52900695800781</v>
       </c>
     </row>
-    <row r="724" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A724">
         <v>201803</v>
       </c>
@@ -35502,7 +35498,7 @@
         <v>249.57699584960938</v>
       </c>
     </row>
-    <row r="725" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A725">
         <v>201804</v>
       </c>
@@ -35549,7 +35545,7 @@
         <v>250.22700500488281</v>
       </c>
     </row>
-    <row r="726" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A726">
         <v>201805</v>
       </c>
@@ -35596,7 +35592,7 @@
         <v>250.79200744628906</v>
       </c>
     </row>
-    <row r="727" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A727">
         <v>201806</v>
       </c>
@@ -35643,7 +35639,7 @@
         <v>251.01800537109375</v>
       </c>
     </row>
-    <row r="728" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A728">
         <v>201807</v>
       </c>
@@ -35690,7 +35686,7 @@
         <v>251.21400451660156</v>
       </c>
     </row>
-    <row r="729" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A729">
         <v>201808</v>
       </c>
@@ -35737,7 +35733,7 @@
         <v>251.66299438476563</v>
       </c>
     </row>
-    <row r="730" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A730">
         <v>201809</v>
       </c>
@@ -35784,7 +35780,7 @@
         <v>252.1820068359375</v>
       </c>
     </row>
-    <row r="731" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A731">
         <v>201810</v>
       </c>
@@ -35831,7 +35827,7 @@
         <v>252.77200317382813</v>
       </c>
     </row>
-    <row r="732" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A732">
         <v>201811</v>
       </c>
@@ -35878,7 +35874,7 @@
         <v>252.593994140625</v>
       </c>
     </row>
-    <row r="733" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A733">
         <v>201812</v>
       </c>
@@ -35925,7 +35921,7 @@
         <v>252.76699829101563</v>
       </c>
     </row>
-    <row r="734" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A734">
         <v>201901</v>
       </c>
@@ -35972,7 +35968,7 @@
         <v>252.56100463867188</v>
       </c>
     </row>
-    <row r="735" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A735">
         <v>201902</v>
       </c>
@@ -36019,7 +36015,7 @@
         <v>253.31900024414063</v>
       </c>
     </row>
-    <row r="736" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A736">
         <v>201903</v>
       </c>
@@ -36066,7 +36062,7 @@
         <v>254.27699279785156</v>
       </c>
     </row>
-    <row r="737" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A737">
         <v>201904</v>
       </c>
@@ -36113,7 +36109,7 @@
         <v>255.23300170898438</v>
       </c>
     </row>
-    <row r="738" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A738">
         <v>201905</v>
       </c>
@@ -36160,7 +36156,7 @@
         <v>255.29600524902344</v>
       </c>
     </row>
-    <row r="739" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A739">
         <v>201906</v>
       </c>
@@ -36207,7 +36203,7 @@
         <v>255.21299743652344</v>
       </c>
     </row>
-    <row r="740" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A740">
         <v>201907</v>
       </c>
@@ -36254,7 +36250,7 @@
         <v>255.802001953125</v>
       </c>
     </row>
-    <row r="741" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A741">
         <v>201908</v>
       </c>
@@ -36301,7 +36297,7 @@
         <v>256.0360107421875</v>
       </c>
     </row>
-    <row r="742" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A742">
         <v>201909</v>
       </c>
@@ -36348,7 +36344,7 @@
         <v>256.42999267578125</v>
       </c>
     </row>
-    <row r="743" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A743">
         <v>201910</v>
       </c>
@@ -36395,7 +36391,7 @@
         <v>257.15499877929688</v>
       </c>
     </row>
-    <row r="744" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A744">
         <v>201911</v>
       </c>
@@ -36442,7 +36438,7 @@
         <v>257.87899780273438</v>
       </c>
     </row>
-    <row r="745" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A745">
         <v>201912</v>
       </c>
@@ -36489,7 +36485,7 @@
         <v>258.6300048828125</v>
       </c>
     </row>
-    <row r="746" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A746">
         <v>202001</v>
       </c>
@@ -36536,7 +36532,7 @@
         <v>259.12701416015625</v>
       </c>
     </row>
-    <row r="747" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A747">
         <v>202002</v>
       </c>
@@ -36583,7 +36579,7 @@
         <v>259.25</v>
       </c>
     </row>
-    <row r="748" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A748">
         <v>202003</v>
       </c>
@@ -36630,7 +36626,7 @@
         <v>258.07598876953125</v>
       </c>
     </row>
-    <row r="749" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A749">
         <v>202004</v>
       </c>
@@ -36677,7 +36673,7 @@
         <v>256.03201293945313</v>
       </c>
     </row>
-    <row r="750" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A750">
         <v>202005</v>
       </c>
@@ -36724,7 +36720,7 @@
         <v>255.802001953125</v>
       </c>
     </row>
-    <row r="751" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A751">
         <v>202006</v>
       </c>
@@ -36771,7 +36767,7 @@
         <v>257.0419921875</v>
       </c>
     </row>
-    <row r="752" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A752">
         <v>202007</v>
       </c>
@@ -36818,7 +36814,7 @@
         <v>258.35198974609375</v>
       </c>
     </row>
-    <row r="753" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A753">
         <v>202008</v>
       </c>
@@ -36865,7 +36861,7 @@
         <v>259.31600952148438</v>
       </c>
     </row>
-    <row r="754" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A754">
         <v>202009</v>
       </c>
@@ -36912,7 +36908,7 @@
         <v>259.99700927734375</v>
       </c>
     </row>
-    <row r="755" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A755">
         <v>202010</v>
       </c>
@@ -36959,7 +36955,7 @@
         <v>260.31900024414063</v>
       </c>
     </row>
-    <row r="756" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A756">
         <v>202011</v>
       </c>
@@ -37006,7 +37002,7 @@
         <v>260.9110107421875</v>
       </c>
     </row>
-    <row r="757" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A757">
         <v>202012</v>
       </c>
@@ -37053,7 +37049,7 @@
         <v>262.04501342773438</v>
       </c>
     </row>
-    <row r="758" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A758">
         <v>202101</v>
       </c>
@@ -37100,7 +37096,7 @@
         <v>262.63900756835938</v>
       </c>
     </row>
-    <row r="759" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A759">
         <v>202102</v>
       </c>
@@ -37147,7 +37143,7 @@
         <v>263.572998046875</v>
       </c>
     </row>
-    <row r="760" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A760" s="8">
         <v>202103</v>
       </c>
@@ -37194,7 +37190,7 @@
         <v>264.84698486328125</v>
       </c>
     </row>
-    <row r="761" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A761" s="23">
         <v>202104</v>
       </c>
@@ -37241,7 +37237,7 @@
         <v>266.625</v>
       </c>
     </row>
-    <row r="762" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A762" s="38">
         <v>202105</v>
       </c>
@@ -37288,7 +37284,7 @@
         <v>268.40399169921875</v>
       </c>
     </row>
-    <row r="763" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A763" s="53">
         <v>202106</v>
       </c>
@@ -37335,7 +37331,7 @@
         <v>270.70999145507813</v>
       </c>
     </row>
-    <row r="764" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A764" s="68">
         <v>202107</v>
       </c>
@@ -37382,7 +37378,7 @@
         <v>271.96499633789063</v>
       </c>
     </row>
-    <row r="765" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A765">
         <v>202108</v>
       </c>
@@ -37429,7 +37425,7 @@
         <v>272.75201416015625</v>
       </c>
     </row>
-    <row r="766" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A766">
         <v>202109</v>
       </c>
@@ -37476,7 +37472,7 @@
         <v>273.94198608398438</v>
       </c>
     </row>
-    <row r="767" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A767">
         <v>202110</v>
       </c>
@@ -37523,7 +37519,7 @@
         <v>276.52801513671875</v>
       </c>
     </row>
-    <row r="768" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A768">
         <v>202111</v>
       </c>
@@ -37570,7 +37566,7 @@
         <v>278.82400512695313</v>
       </c>
     </row>
-    <row r="769" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A769">
         <v>202112</v>
       </c>
@@ -37617,7 +37613,7 @@
         <v>280.80599975585938</v>
       </c>
     </row>
-    <row r="770" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A770">
         <v>202201</v>
       </c>
@@ -37664,7 +37660,7 @@
         <v>282.5419921875</v>
       </c>
     </row>
-    <row r="771" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A771">
         <v>202202</v>
       </c>
@@ -37711,7 +37707,7 @@
         <v>284.52499389648438</v>
       </c>
     </row>
-    <row r="772" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A772">
         <v>202203</v>
       </c>
@@ -37758,7 +37754,7 @@
         <v>287.46701049804688</v>
       </c>
     </row>
-    <row r="773" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A773">
         <v>202204</v>
       </c>
@@ -37805,7 +37801,7 @@
         <v>288.58200073242188</v>
       </c>
     </row>
-    <row r="774" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A774">
         <v>202205</v>
       </c>
@@ -37852,7 +37848,7 @@
         <v>291.29901123046875</v>
       </c>
     </row>
-    <row r="775" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A775">
         <v>202206</v>
       </c>
@@ -37899,7 +37895,7 @@
         <v>295.07199096679688</v>
       </c>
     </row>
-    <row r="776" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A776">
         <v>202207</v>
       </c>
@@ -37946,7 +37942,7 @@
         <v>294.94000244140625</v>
       </c>
     </row>
-    <row r="777" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A777">
         <v>202208</v>
       </c>
@@ -37993,7 +37989,7 @@
         <v>295.1619873046875</v>
       </c>
     </row>
-    <row r="778" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A778">
         <v>202209</v>
       </c>
@@ -38040,7 +38036,7 @@
         <v>296.42098999023438</v>
       </c>
     </row>
-    <row r="779" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A779">
         <v>202210</v>
       </c>
@@ -38087,7 +38083,7 @@
         <v>297.97900390625</v>
       </c>
     </row>
-    <row r="780" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A780">
         <v>202211</v>
       </c>
@@ -38134,7 +38130,7 @@
         <v>298.7080078125</v>
       </c>
     </row>
-    <row r="781" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A781">
         <v>202212</v>
       </c>
@@ -38181,7 +38177,7 @@
         <v>298.80801391601563</v>
       </c>
     </row>
-    <row r="782" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A782">
         <v>202301</v>
       </c>
@@ -38228,7 +38224,7 @@
         <v>300.45599365234375</v>
       </c>
     </row>
-    <row r="783" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A783">
         <v>202302</v>
       </c>
@@ -38275,7 +38271,7 @@
         <v>301.47601318359375</v>
       </c>
     </row>
-    <row r="784" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A784">
         <v>202303</v>
       </c>
@@ -38322,7 +38318,7 @@
         <v>301.64300537109375</v>
       </c>
     </row>
-    <row r="785" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A785">
         <v>202304</v>
       </c>
@@ -38369,7 +38365,7 @@
         <v>302.85800170898438</v>
       </c>
     </row>
-    <row r="786" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A786">
         <v>202305</v>
       </c>
@@ -38416,7 +38412,7 @@
         <v>303.31600952148438</v>
       </c>
     </row>
-    <row r="787" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A787">
         <v>202306</v>
       </c>
@@ -38463,7 +38459,7 @@
         <v>304.0989990234375</v>
       </c>
     </row>
-    <row r="788" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A788">
         <v>202307</v>
       </c>
@@ -38510,7 +38506,7 @@
         <v>304.614990234375</v>
       </c>
     </row>
-    <row r="789" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A789">
         <v>202308</v>
       </c>
@@ -38557,7 +38553,7 @@
         <v>306.13800048828125</v>
       </c>
     </row>
-    <row r="790" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A790">
         <v>202309</v>
       </c>
@@ -38604,7 +38600,7 @@
         <v>307.37399291992188</v>
       </c>
     </row>
-    <row r="791" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A791">
         <v>202310</v>
       </c>
@@ -38651,7 +38647,7 @@
         <v>307.65301513671875</v>
       </c>
     </row>
-    <row r="792" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A792">
         <v>202311</v>
       </c>
@@ -38698,7 +38694,7 @@
         <v>308.08700561523438</v>
       </c>
     </row>
-    <row r="793" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A793">
         <v>202312</v>
       </c>
@@ -38742,7 +38738,7 @@
         <v>308.7349853515625</v>
       </c>
     </row>
-    <row r="794" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A794">
         <v>202401</v>
       </c>
@@ -38789,7 +38785,7 @@
         <v>309.79400634765625</v>
       </c>
     </row>
-    <row r="795" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A795">
         <v>202402</v>
       </c>
@@ -38836,7 +38832,7 @@
         <v>311.02200317382813</v>
       </c>
     </row>
-    <row r="796" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A796">
         <v>202403</v>
       </c>
@@ -38883,7 +38879,7 @@
         <v>312.10699462890625</v>
       </c>
     </row>
-    <row r="797" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A797">
         <v>202404</v>
       </c>
@@ -38930,7 +38926,7 @@
         <v>313.0159912109375</v>
       </c>
     </row>
-    <row r="798" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A798">
         <v>202405</v>
       </c>
@@ -38977,7 +38973,7 @@
         <v>313.1400146484375</v>
       </c>
     </row>
-    <row r="799" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A799">
         <v>202406</v>
       </c>
@@ -39024,7 +39020,7 @@
         <v>313.13101196289063</v>
       </c>
     </row>
-    <row r="800" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A800">
         <v>202407</v>
       </c>
@@ -39071,7 +39067,7 @@
         <v>313.56600952148438</v>
       </c>
     </row>
-    <row r="801" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A801">
         <v>202408</v>
       </c>
@@ -39118,7 +39114,7 @@
         <v>314.13101196289063</v>
       </c>
     </row>
-    <row r="802" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A802">
         <v>202409</v>
       </c>
@@ -39165,7 +39161,7 @@
         <v>314.85101318359375</v>
       </c>
     </row>
-    <row r="803" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A803">
         <v>202410</v>
       </c>
@@ -39212,7 +39208,7 @@
         <v>315.56399536132813</v>
       </c>
     </row>
-    <row r="804" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A804">
         <v>202411</v>
       </c>
@@ -39259,7 +39255,7 @@
         <v>316.44900512695313</v>
       </c>
     </row>
-    <row r="805" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A805">
         <v>202412</v>
       </c>
@@ -39304,6 +39300,564 @@
       </c>
       <c r="O805">
         <v>317.60299682617188</v>
+      </c>
+    </row>
+    <row r="806" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A806">
+        <v>202501</v>
+      </c>
+      <c r="B806">
+        <v>-0.39626079797744751</v>
+      </c>
+      <c r="C806">
+        <v>-0.22127482295036316</v>
+      </c>
+      <c r="D806">
+        <v>-3.877957905889029</v>
+      </c>
+      <c r="E806">
+        <v>14.3</v>
+      </c>
+      <c r="F806">
+        <v>27</v>
+      </c>
+      <c r="G806">
+        <v>6.4280131250000005</v>
+      </c>
+      <c r="H806">
+        <v>7.5484217360427541E-2</v>
+      </c>
+      <c r="I806">
+        <v>100.064697265625</v>
+      </c>
+      <c r="J806">
+        <v>2198</v>
+      </c>
+      <c r="K806">
+        <v>4185.10009765625</v>
+      </c>
+      <c r="L806">
+        <v>14079.099609375</v>
+      </c>
+      <c r="M806">
+        <v>0</v>
+      </c>
+      <c r="N806">
+        <v>158268</v>
+      </c>
+      <c r="O806">
+        <v>318.96099853515625</v>
+      </c>
+    </row>
+    <row r="807" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A807">
+        <v>202502</v>
+      </c>
+      <c r="B807">
+        <v>-0.49838057160377502</v>
+      </c>
+      <c r="C807">
+        <v>-0.30807152390480042</v>
+      </c>
+      <c r="D807">
+        <v>6.6639447311291118</v>
+      </c>
+      <c r="E807">
+        <v>11.8</v>
+      </c>
+      <c r="F807">
+        <v>29</v>
+      </c>
+      <c r="G807">
+        <v>8.3801925000000015</v>
+      </c>
+      <c r="H807">
+        <v>7.688354502178428E-2</v>
+      </c>
+      <c r="I807">
+        <v>101.09929656982422</v>
+      </c>
+      <c r="J807">
+        <v>2209.199951171875</v>
+      </c>
+      <c r="K807">
+        <v>4209.2001953125</v>
+      </c>
+      <c r="L807">
+        <v>14101.400390625</v>
+      </c>
+      <c r="M807">
+        <v>0</v>
+      </c>
+      <c r="N807">
+        <v>158310</v>
+      </c>
+      <c r="O807">
+        <v>319.67898559570313</v>
+      </c>
+    </row>
+    <row r="808" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A808">
+        <v>202503</v>
+      </c>
+      <c r="B808">
+        <v>-0.45248204469680786</v>
+      </c>
+      <c r="C808">
+        <v>-0.36197319626808167</v>
+      </c>
+      <c r="D808">
+        <v>8.3437074511527705</v>
+      </c>
+      <c r="E808">
+        <v>147.1</v>
+      </c>
+      <c r="F808">
+        <v>19</v>
+      </c>
+      <c r="G808">
+        <v>7.4192287499999994</v>
+      </c>
+      <c r="H808">
+        <v>7.4558881361717289E-2</v>
+      </c>
+      <c r="I808">
+        <v>101.04039764404297</v>
+      </c>
+      <c r="J808">
+        <v>2300.199951171875</v>
+      </c>
+      <c r="K808">
+        <v>4195.2001953125</v>
+      </c>
+      <c r="L808">
+        <v>14187.5</v>
+      </c>
+      <c r="M808">
+        <v>0</v>
+      </c>
+      <c r="N808">
+        <v>158377</v>
+      </c>
+      <c r="O808">
+        <v>319.78500366210938</v>
+      </c>
+    </row>
+    <row r="809" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A809">
+        <v>202504</v>
+      </c>
+      <c r="B809">
+        <v>-0.65012437105178833</v>
+      </c>
+      <c r="C809">
+        <v>-0.53775376081466675</v>
+      </c>
+      <c r="D809">
+        <v>6.7923988572527572</v>
+      </c>
+      <c r="E809">
+        <v>126.1</v>
+      </c>
+      <c r="F809">
+        <v>33</v>
+      </c>
+      <c r="G809">
+        <v>7.9743562500000023</v>
+      </c>
+      <c r="H809">
+        <v>7.4809795182607303E-2</v>
+      </c>
+      <c r="I809">
+        <v>101.12789916992188</v>
+      </c>
+      <c r="J809">
+        <v>2296.60009765625</v>
+      </c>
+      <c r="K809">
+        <v>4191.10009765625</v>
+      </c>
+      <c r="L809">
+        <v>14258.599609375</v>
+      </c>
+      <c r="M809">
+        <v>0</v>
+      </c>
+      <c r="N809">
+        <v>158485</v>
+      </c>
+      <c r="O809">
+        <v>320.302001953125</v>
+      </c>
+    </row>
+    <row r="810" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A810">
+        <v>202505</v>
+      </c>
+      <c r="B810">
+        <v>-0.66038382053375244</v>
+      </c>
+      <c r="C810">
+        <v>-0.51309466361999512</v>
+      </c>
+      <c r="D810">
+        <v>6.0814457538300175</v>
+      </c>
+      <c r="E810">
+        <v>19.5</v>
+      </c>
+      <c r="F810">
+        <v>35</v>
+      </c>
+      <c r="G810">
+        <v>7.4809718749999981</v>
+      </c>
+      <c r="H810">
+        <v>7.5469620009477545E-2</v>
+      </c>
+      <c r="I810">
+        <v>100.96549987792969</v>
+      </c>
+      <c r="J810">
+        <v>2247</v>
+      </c>
+      <c r="K810">
+        <v>4190.2998046875</v>
+      </c>
+      <c r="L810">
+        <v>14317.7998046875</v>
+      </c>
+      <c r="M810">
+        <v>0</v>
+      </c>
+      <c r="N810">
+        <v>158498</v>
+      </c>
+      <c r="O810">
+        <v>320.6199951171875</v>
+      </c>
+    </row>
+    <row r="811" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A811">
+        <v>202506</v>
+      </c>
+      <c r="B811">
+        <v>-0.65319973230361938</v>
+      </c>
+      <c r="C811">
+        <v>-0.46892443299293518</v>
+      </c>
+      <c r="D811">
+        <v>7.2683506859941405</v>
+      </c>
+      <c r="E811">
+        <v>53</v>
+      </c>
+      <c r="F811">
+        <v>26</v>
+      </c>
+      <c r="G811">
+        <v>7.5253581249999995</v>
+      </c>
+      <c r="H811">
+        <v>7.7841155414929336E-2</v>
+      </c>
+      <c r="I811">
+        <v>101.47850036621094</v>
+      </c>
+      <c r="J811">
+        <v>2253.60009765625</v>
+      </c>
+      <c r="K811">
+        <v>4234.7998046875</v>
+      </c>
+      <c r="L811">
+        <v>14380</v>
+      </c>
+      <c r="M811">
+        <v>0</v>
+      </c>
+      <c r="N811">
+        <v>158478</v>
+      </c>
+      <c r="O811">
+        <v>321.43499755859375</v>
+      </c>
+    </row>
+    <row r="812" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A812">
+        <v>202507</v>
+      </c>
+      <c r="B812">
+        <v>-0.65427249670028687</v>
+      </c>
+      <c r="C812">
+        <v>-0.56589937210083008</v>
+      </c>
+      <c r="D812">
+        <v>9.8723788529494261</v>
+      </c>
+      <c r="E812">
+        <v>24.1</v>
+      </c>
+      <c r="F812">
+        <v>37</v>
+      </c>
+      <c r="G812">
+        <v>7.7751206249999996</v>
+      </c>
+      <c r="H812">
+        <v>7.8927678719837982E-2</v>
+      </c>
+      <c r="I812">
+        <v>101.89399719238281</v>
+      </c>
+      <c r="J812">
+        <v>2280.300048828125</v>
+      </c>
+      <c r="K812">
+        <v>4241.2998046875</v>
+      </c>
+      <c r="L812">
+        <v>14485.7001953125</v>
+      </c>
+      <c r="M812">
+        <v>0</v>
+      </c>
+      <c r="N812">
+        <v>158542</v>
+      </c>
+      <c r="O812">
+        <v>322.16900634765625</v>
+      </c>
+    </row>
+    <row r="813" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A813">
+        <v>202508</v>
+      </c>
+      <c r="B813">
+        <v>-0.60775458812713623</v>
+      </c>
+      <c r="C813">
+        <v>-0.45033624768257141</v>
+      </c>
+      <c r="D813">
+        <v>10.158897713824821</v>
+      </c>
+      <c r="E813">
+        <v>27.2</v>
+      </c>
+      <c r="F813">
+        <v>28</v>
+      </c>
+      <c r="G813">
+        <v>7.6087099999999968</v>
+      </c>
+      <c r="H813">
+        <v>8.0356325355688901E-2</v>
+      </c>
+      <c r="I813">
+        <v>101.62470245361328</v>
+      </c>
+      <c r="J813">
+        <v>2281.800048828125</v>
+      </c>
+      <c r="K813">
+        <v>4273.7998046875</v>
+      </c>
+      <c r="L813">
+        <v>14568.2001953125</v>
+      </c>
+      <c r="M813">
+        <v>0</v>
+      </c>
+      <c r="N813">
+        <v>158472</v>
+      </c>
+      <c r="O813">
+        <v>323.29098510742188</v>
+      </c>
+    </row>
+    <row r="814" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A814">
+        <v>202509</v>
+      </c>
+      <c r="B814">
+        <v>-0.53953444957733154</v>
+      </c>
+      <c r="C814">
+        <v>-0.42798230051994324</v>
+      </c>
+      <c r="D814">
+        <v>9.4744052551709359</v>
+      </c>
+      <c r="E814">
+        <v>14.6</v>
+      </c>
+      <c r="F814">
+        <v>31</v>
+      </c>
+      <c r="G814">
+        <v>7.7353456250000008</v>
+      </c>
+      <c r="H814">
+        <v>7.8465894190094213E-2</v>
+      </c>
+      <c r="I814">
+        <v>101.66799926757813</v>
+      </c>
+      <c r="J814">
+        <v>2269.800048828125</v>
+      </c>
+      <c r="K814">
+        <v>4289.89990234375</v>
+      </c>
+      <c r="L814">
+        <v>14642.7001953125</v>
+      </c>
+      <c r="M814">
+        <v>0</v>
+      </c>
+      <c r="N814">
+        <v>158548</v>
+      </c>
+      <c r="O814">
+        <v>324.2449951171875</v>
+      </c>
+    </row>
+    <row r="815" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A815">
+        <v>202510</v>
+      </c>
+      <c r="B815">
+        <v>-0.38906139135360718</v>
+      </c>
+      <c r="D815">
+        <v>9.4263663210271567</v>
+      </c>
+      <c r="E815">
+        <v>5.2</v>
+      </c>
+      <c r="F815">
+        <v>35</v>
+      </c>
+      <c r="G815">
+        <v>6.5409299999999977</v>
+      </c>
+      <c r="H815">
+        <v>7.16109092363858E-2</v>
+      </c>
+      <c r="I815">
+        <v>101.20749664306641</v>
+      </c>
+      <c r="J815">
+        <v>2271.300048828125</v>
+      </c>
+      <c r="K815">
+        <v>4289.60009765625</v>
+      </c>
+      <c r="L815">
+        <v>14726.7998046875</v>
+      </c>
+      <c r="M815">
+        <v>0</v>
+      </c>
+      <c r="N815">
+        <v>158408</v>
+      </c>
+    </row>
+    <row r="816" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A816">
+        <v>202511</v>
+      </c>
+      <c r="B816">
+        <v>-0.27099928259849548</v>
+      </c>
+      <c r="C816">
+        <v>-0.27260804176330566</v>
+      </c>
+      <c r="D816">
+        <v>12.570042580843555</v>
+      </c>
+      <c r="E816">
+        <v>15.9</v>
+      </c>
+      <c r="F816">
+        <v>19</v>
+      </c>
+      <c r="G816">
+        <v>7.0046712500000003</v>
+      </c>
+      <c r="H816">
+        <v>7.5073642923189687E-2</v>
+      </c>
+      <c r="I816">
+        <v>101.36049652099609</v>
+      </c>
+      <c r="J816">
+        <v>2288.89990234375</v>
+      </c>
+      <c r="K816">
+        <v>4304.10009765625</v>
+      </c>
+      <c r="L816">
+        <v>14768.099609375</v>
+      </c>
+      <c r="M816">
+        <v>0</v>
+      </c>
+      <c r="N816">
+        <v>158449</v>
+      </c>
+      <c r="O816">
+        <v>325.06298828125</v>
+      </c>
+    </row>
+    <row r="817" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A817">
+        <v>202512</v>
+      </c>
+      <c r="B817">
+        <v>0.12571176886558533</v>
+      </c>
+      <c r="C817">
+        <v>0.15276879072189331</v>
+      </c>
+      <c r="D817">
+        <v>11.812472392766571</v>
+      </c>
+      <c r="E817">
+        <v>10.6</v>
+      </c>
+      <c r="F817">
+        <v>33</v>
+      </c>
+      <c r="G817">
+        <v>5.750628124999996</v>
+      </c>
+      <c r="H817">
+        <v>7.77534532844774E-2</v>
+      </c>
+      <c r="I817">
+        <v>101.6781005859375</v>
+      </c>
+      <c r="J817">
+        <v>2285.300048828125</v>
+      </c>
+      <c r="K817">
+        <v>4312.2998046875</v>
+      </c>
+      <c r="L817">
+        <v>14857.900390625</v>
+      </c>
+      <c r="M817">
+        <v>0</v>
+      </c>
+      <c r="N817">
+        <v>158432</v>
+      </c>
+      <c r="O817">
+        <v>326.031005859375</v>
       </c>
     </row>
   </sheetData>
@@ -39314,7 +39868,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E508FB28-1994-4F80-A567-6586BD6DD530}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
